--- a/Другое/study_chart_copy.xlsx
+++ b/Другое/study_chart_copy.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="34">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -124,6 +124,12 @@
   </si>
   <si>
     <t>Чтение перед сном</t>
+  </si>
+  <si>
+    <t>Не сидеть утром в телефоне</t>
+  </si>
+  <si>
+    <t>Спорт (хотя бы одно упражнение)</t>
   </si>
 </sst>
 </file>
@@ -564,7 +570,14 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA7FFA7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1241,12 +1254,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1257,30 +1270,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H9:AD42"/>
+  <dimension ref="H9:AF42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="1"/>
     <col min="8" max="8" width="5" style="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" style="1" customWidth="1"/>
     <col min="10" max="11" width="16.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="24.140625" style="1" customWidth="1"/>
-    <col min="13" max="16" width="14.28515625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.5703125" style="1" customWidth="1"/>
-    <col min="18" max="19" width="23.28515625" style="1" customWidth="1"/>
-    <col min="20" max="21" width="11.28515625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="21.28515625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="11.5703125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" customWidth="1"/>
-    <col min="25" max="26" width="10" style="1" customWidth="1"/>
-    <col min="27" max="27" width="14.140625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="13.85546875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="18.42578125" style="1" customWidth="1"/>
-    <col min="30" max="30" width="18" style="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="13" width="24.140625" style="1" customWidth="1"/>
+    <col min="14" max="17" width="14.28515625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20.5703125" style="1" customWidth="1"/>
+    <col min="19" max="20" width="23.28515625" style="1" customWidth="1"/>
+    <col min="21" max="22" width="11.28515625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="30.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" customWidth="1"/>
+    <col min="26" max="27" width="10" style="1" customWidth="1"/>
+    <col min="28" max="28" width="20.5703125" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.140625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="13.85546875" style="1" customWidth="1"/>
+    <col min="31" max="31" width="18.42578125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="18" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:30" ht="45" customHeight="1">
+    <row r="9" spans="8:32" ht="45" customHeight="1">
       <c r="H9" s="47" t="s">
         <v>0</v>
       </c>
@@ -1306,8 +1320,10 @@
       <c r="AB9" s="48"/>
       <c r="AC9" s="48"/>
       <c r="AD9" s="48"/>
-    </row>
-    <row r="10" spans="8:30" ht="30" customHeight="1">
+      <c r="AE9" s="48"/>
+      <c r="AF9" s="48"/>
+    </row>
+    <row r="10" spans="8:32" ht="30" customHeight="1">
       <c r="H10" s="10" t="s">
         <v>1</v>
       </c>
@@ -1323,62 +1339,68 @@
       <c r="L10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="19" t="s">
+      <c r="M10" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="N10" s="20" t="s">
+      <c r="O10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="20" t="s">
+      <c r="P10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="P10" s="20" t="s">
+      <c r="Q10" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="20" t="s">
+      <c r="R10" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="22" t="s">
+      <c r="S10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="22" t="s">
+      <c r="T10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="T10" s="23" t="s">
+      <c r="U10" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="U10" s="23" t="s">
+      <c r="V10" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="V10" s="22" t="s">
+      <c r="W10" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="W10" s="24" t="s">
+      <c r="X10" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="X10" s="25" t="s">
+      <c r="Y10" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="Y10" s="24" t="s">
+      <c r="Z10" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z10" s="32" t="s">
+      <c r="AA10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="AA10" s="34" t="s">
+      <c r="AB10" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC10" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="AB10" s="35" t="s">
+      <c r="AD10" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="AC10" s="35" t="s">
+      <c r="AE10" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="AD10" s="26" t="s">
+      <c r="AF10" s="26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="8:30" ht="15.75">
+    <row r="11" spans="8:32" ht="15.75">
       <c r="H11" s="27">
         <v>1</v>
       </c>
@@ -1390,15 +1412,15 @@
       </c>
       <c r="K11" s="29"/>
       <c r="L11" s="29"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="30"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="31"/>
       <c r="P11" s="30"/>
       <c r="Q11" s="30"/>
-      <c r="R11" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="S11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="31" t="s">
+        <v>12</v>
+      </c>
       <c r="T11" s="30"/>
       <c r="U11" s="30"/>
       <c r="V11" s="30"/>
@@ -1406,15 +1428,17 @@
       <c r="X11" s="30"/>
       <c r="Y11" s="30"/>
       <c r="Z11" s="30"/>
-      <c r="AA11" s="33"/>
+      <c r="AA11" s="30"/>
       <c r="AB11" s="33"/>
       <c r="AC11" s="33"/>
-      <c r="AD11" s="36">
-        <f>COUNTA(K11:AC11)</f>
+      <c r="AD11" s="33"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="36">
+        <f>COUNTA(K11:AE11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="8:30" ht="15.75">
+    <row r="12" spans="8:32" ht="15.75">
       <c r="H12" s="27">
         <v>2</v>
       </c>
@@ -1426,19 +1450,19 @@
       </c>
       <c r="K12" s="29"/>
       <c r="L12" s="29"/>
-      <c r="M12" s="30"/>
+      <c r="M12" s="29"/>
       <c r="N12" s="30"/>
       <c r="O12" s="30"/>
       <c r="P12" s="30"/>
       <c r="Q12" s="30"/>
-      <c r="R12" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="U12" s="30"/>
+      <c r="R12" s="30"/>
+      <c r="S12" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="T12" s="30"/>
+      <c r="U12" s="30" t="s">
+        <v>12</v>
+      </c>
       <c r="V12" s="30"/>
       <c r="W12" s="30"/>
       <c r="X12" s="30"/>
@@ -1446,15 +1470,17 @@
       <c r="Z12" s="30"/>
       <c r="AA12" s="30"/>
       <c r="AB12" s="30"/>
-      <c r="AC12" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD12" s="36">
-        <f t="shared" ref="AD12:AD41" si="0">COUNTA(K12:AC12)</f>
+      <c r="AC12" s="30"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF12" s="36">
+        <f t="shared" ref="AF12:AF41" si="0">COUNTA(K12:AE12)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="8:30" ht="15.75">
+    <row r="13" spans="8:32" ht="15.75">
       <c r="H13" s="27">
         <v>3</v>
       </c>
@@ -1470,9 +1496,7 @@
       <c r="L13" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="M13" s="31" t="s">
-        <v>12</v>
-      </c>
+      <c r="M13" s="38"/>
       <c r="N13" s="31" t="s">
         <v>12</v>
       </c>
@@ -1488,23 +1512,27 @@
       <c r="R13" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="S13" s="31"/>
-      <c r="T13" s="30"/>
+      <c r="S13" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="T13" s="31"/>
       <c r="U13" s="30"/>
       <c r="V13" s="30"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="30"/>
+      <c r="W13" s="30"/>
+      <c r="X13" s="31"/>
       <c r="Y13" s="30"/>
       <c r="Z13" s="30"/>
       <c r="AA13" s="30"/>
       <c r="AB13" s="30"/>
       <c r="AC13" s="30"/>
-      <c r="AD13" s="36">
+      <c r="AD13" s="30"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="36">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="8:30" ht="15.75">
+    <row r="14" spans="8:32" ht="15.75">
       <c r="H14" s="27">
         <v>4</v>
       </c>
@@ -1516,33 +1544,35 @@
       </c>
       <c r="K14" s="39"/>
       <c r="L14" s="39"/>
-      <c r="M14" s="31"/>
+      <c r="M14" s="39"/>
       <c r="N14" s="31"/>
-      <c r="O14" s="31" t="s">
-        <v>12</v>
-      </c>
+      <c r="O14" s="31"/>
       <c r="P14" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="Q14" s="31"/>
+      <c r="Q14" s="31" t="s">
+        <v>12</v>
+      </c>
       <c r="R14" s="31"/>
       <c r="S14" s="31"/>
-      <c r="T14" s="30"/>
+      <c r="T14" s="31"/>
       <c r="U14" s="30"/>
       <c r="V14" s="30"/>
-      <c r="W14" s="31"/>
-      <c r="X14" s="30"/>
+      <c r="W14" s="30"/>
+      <c r="X14" s="31"/>
       <c r="Y14" s="30"/>
       <c r="Z14" s="30"/>
       <c r="AA14" s="30"/>
       <c r="AB14" s="30"/>
       <c r="AC14" s="30"/>
-      <c r="AD14" s="36">
+      <c r="AD14" s="30"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="36">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="8:30" ht="15.75">
+    <row r="15" spans="8:32" ht="15.75">
       <c r="H15" s="27">
         <v>5</v>
       </c>
@@ -1554,17 +1584,17 @@
       </c>
       <c r="K15" s="39"/>
       <c r="L15" s="39"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30" t="s">
-        <v>12</v>
-      </c>
+      <c r="M15" s="39"/>
+      <c r="N15" s="30"/>
       <c r="O15" s="30" t="s">
         <v>12</v>
       </c>
       <c r="P15" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="Q15" s="30"/>
+      <c r="Q15" s="30" t="s">
+        <v>12</v>
+      </c>
       <c r="R15" s="30"/>
       <c r="S15" s="30"/>
       <c r="T15" s="30"/>
@@ -1577,12 +1607,14 @@
       <c r="AA15" s="30"/>
       <c r="AB15" s="30"/>
       <c r="AC15" s="30"/>
-      <c r="AD15" s="36">
+      <c r="AD15" s="30"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="36">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="8:30" ht="15.75">
+    <row r="16" spans="8:32" ht="15.75">
       <c r="H16" s="27">
         <v>6</v>
       </c>
@@ -1598,11 +1630,9 @@
       <c r="L16" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="30"/>
+      <c r="M16" s="39"/>
       <c r="N16" s="30"/>
-      <c r="O16" s="30" t="s">
-        <v>12</v>
-      </c>
+      <c r="O16" s="30"/>
       <c r="P16" s="30" t="s">
         <v>12</v>
       </c>
@@ -1615,7 +1645,9 @@
       <c r="S16" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="T16" s="30"/>
+      <c r="T16" s="30" t="s">
+        <v>12</v>
+      </c>
       <c r="U16" s="30"/>
       <c r="V16" s="30"/>
       <c r="W16" s="30"/>
@@ -1624,15 +1656,17 @@
       <c r="Z16" s="30"/>
       <c r="AA16" s="30"/>
       <c r="AB16" s="30"/>
-      <c r="AC16" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD16" s="36">
+      <c r="AC16" s="30"/>
+      <c r="AD16" s="30"/>
+      <c r="AE16" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF16" s="36">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="8:30" ht="15.75">
+    <row r="17" spans="8:32" ht="15.75">
       <c r="H17" s="27">
         <v>7</v>
       </c>
@@ -1646,35 +1680,43 @@
       <c r="L17" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="M17" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="N17" s="31"/>
-      <c r="O17" s="30" t="s">
-        <v>12</v>
-      </c>
+      <c r="M17" s="39"/>
+      <c r="N17" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="O17" s="31"/>
       <c r="P17" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="15"/>
-      <c r="X17" s="15"/>
-      <c r="Y17" s="15"/>
-      <c r="Z17" s="15"/>
-      <c r="AA17" s="15"/>
-      <c r="AB17" s="15"/>
-      <c r="AC17" s="15"/>
-      <c r="AD17" s="36">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="8:30" ht="15.75">
+      <c r="Q17" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="R17" s="31"/>
+      <c r="S17" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="T17" s="30"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="30"/>
+      <c r="Z17" s="30"/>
+      <c r="AA17" s="30"/>
+      <c r="AB17" s="30"/>
+      <c r="AC17" s="30"/>
+      <c r="AD17" s="30"/>
+      <c r="AE17" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF17" s="36">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="8:32" ht="15.75">
       <c r="H18" s="12">
         <v>8</v>
       </c>
@@ -1684,15 +1726,27 @@
       <c r="J18" s="14">
         <v>46211</v>
       </c>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
+      <c r="K18" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="37"/>
+      <c r="N18" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="15"/>
+      <c r="P18" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="R18" s="16"/>
+      <c r="S18" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="T18" s="15"/>
       <c r="U18" s="15"/>
       <c r="V18" s="15"/>
@@ -1703,12 +1757,14 @@
       <c r="AA18" s="15"/>
       <c r="AB18" s="15"/>
       <c r="AC18" s="15"/>
-      <c r="AD18" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="8:30" ht="15.75">
+      <c r="AD18" s="15"/>
+      <c r="AE18" s="15"/>
+      <c r="AF18" s="36">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="8:32" ht="15.75">
       <c r="H19" s="12">
         <v>9</v>
       </c>
@@ -1720,7 +1776,7 @@
       </c>
       <c r="K19" s="37"/>
       <c r="L19" s="37"/>
-      <c r="M19" s="15"/>
+      <c r="M19" s="37"/>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
       <c r="P19" s="15"/>
@@ -1737,12 +1793,14 @@
       <c r="AA19" s="15"/>
       <c r="AB19" s="15"/>
       <c r="AC19" s="15"/>
-      <c r="AD19" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="8:30" ht="15.75">
+      <c r="AD19" s="15"/>
+      <c r="AE19" s="15"/>
+      <c r="AF19" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="8:32" ht="15.75">
       <c r="H20" s="12">
         <v>10</v>
       </c>
@@ -1754,7 +1812,7 @@
       </c>
       <c r="K20" s="37"/>
       <c r="L20" s="37"/>
-      <c r="M20" s="15"/>
+      <c r="M20" s="37"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
@@ -1771,12 +1829,14 @@
       <c r="AA20" s="15"/>
       <c r="AB20" s="15"/>
       <c r="AC20" s="15"/>
-      <c r="AD20" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="8:30" ht="15.75">
+      <c r="AD20" s="15"/>
+      <c r="AE20" s="15"/>
+      <c r="AF20" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="8:32" ht="15.75">
       <c r="H21" s="12">
         <v>11</v>
       </c>
@@ -1788,12 +1848,12 @@
       </c>
       <c r="K21" s="37"/>
       <c r="L21" s="37"/>
-      <c r="M21" s="16"/>
+      <c r="M21" s="37"/>
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
       <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
-      <c r="R21" s="15"/>
+      <c r="R21" s="16"/>
       <c r="S21" s="15"/>
       <c r="T21" s="15"/>
       <c r="U21" s="15"/>
@@ -1805,12 +1865,14 @@
       <c r="AA21" s="15"/>
       <c r="AB21" s="15"/>
       <c r="AC21" s="15"/>
-      <c r="AD21" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="8:30" ht="15.75">
+      <c r="AD21" s="15"/>
+      <c r="AE21" s="15"/>
+      <c r="AF21" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="8:32" ht="15.75">
       <c r="H22" s="12">
         <v>12</v>
       </c>
@@ -1822,12 +1884,12 @@
       </c>
       <c r="K22" s="37"/>
       <c r="L22" s="37"/>
-      <c r="M22" s="16"/>
+      <c r="M22" s="37"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
-      <c r="R22" s="15"/>
+      <c r="R22" s="16"/>
       <c r="S22" s="15"/>
       <c r="T22" s="15"/>
       <c r="U22" s="15"/>
@@ -1839,12 +1901,14 @@
       <c r="AA22" s="15"/>
       <c r="AB22" s="15"/>
       <c r="AC22" s="15"/>
-      <c r="AD22" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="8:30" ht="15.75">
+      <c r="AD22" s="15"/>
+      <c r="AE22" s="15"/>
+      <c r="AF22" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="8:32" ht="15.75">
       <c r="H23" s="12">
         <v>13</v>
       </c>
@@ -1856,7 +1920,7 @@
       </c>
       <c r="K23" s="37"/>
       <c r="L23" s="37"/>
-      <c r="M23" s="15"/>
+      <c r="M23" s="37"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
@@ -1873,12 +1937,14 @@
       <c r="AA23" s="15"/>
       <c r="AB23" s="15"/>
       <c r="AC23" s="15"/>
-      <c r="AD23" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="8:30" ht="15.75">
+      <c r="AD23" s="15"/>
+      <c r="AE23" s="15"/>
+      <c r="AF23" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="8:32" ht="15.75">
       <c r="H24" s="12">
         <v>14</v>
       </c>
@@ -1890,7 +1956,7 @@
       </c>
       <c r="K24" s="37"/>
       <c r="L24" s="37"/>
-      <c r="M24" s="15"/>
+      <c r="M24" s="37"/>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
@@ -1907,12 +1973,14 @@
       <c r="AA24" s="15"/>
       <c r="AB24" s="15"/>
       <c r="AC24" s="15"/>
-      <c r="AD24" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="8:30" ht="15.75">
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="15"/>
+      <c r="AF24" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="8:32" ht="15.75">
       <c r="H25" s="12">
         <v>15</v>
       </c>
@@ -1924,12 +1992,12 @@
       </c>
       <c r="K25" s="37"/>
       <c r="L25" s="37"/>
-      <c r="M25" s="16"/>
+      <c r="M25" s="37"/>
       <c r="N25" s="16"/>
       <c r="O25" s="16"/>
       <c r="P25" s="16"/>
       <c r="Q25" s="16"/>
-      <c r="R25" s="15"/>
+      <c r="R25" s="16"/>
       <c r="S25" s="15"/>
       <c r="T25" s="15"/>
       <c r="U25" s="15"/>
@@ -1941,12 +2009,14 @@
       <c r="AA25" s="15"/>
       <c r="AB25" s="15"/>
       <c r="AC25" s="15"/>
-      <c r="AD25" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="8:30" ht="15.75">
+      <c r="AD25" s="15"/>
+      <c r="AE25" s="15"/>
+      <c r="AF25" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="8:32" ht="15.75">
       <c r="H26" s="12">
         <v>16</v>
       </c>
@@ -1958,12 +2028,12 @@
       </c>
       <c r="K26" s="37"/>
       <c r="L26" s="37"/>
-      <c r="M26" s="16"/>
+      <c r="M26" s="37"/>
       <c r="N26" s="16"/>
       <c r="O26" s="16"/>
       <c r="P26" s="16"/>
       <c r="Q26" s="16"/>
-      <c r="R26" s="15"/>
+      <c r="R26" s="16"/>
       <c r="S26" s="15"/>
       <c r="T26" s="15"/>
       <c r="U26" s="15"/>
@@ -1975,12 +2045,14 @@
       <c r="AA26" s="15"/>
       <c r="AB26" s="15"/>
       <c r="AC26" s="15"/>
-      <c r="AD26" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="8:30" ht="15.75">
+      <c r="AD26" s="15"/>
+      <c r="AE26" s="15"/>
+      <c r="AF26" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="8:32" ht="15.75">
       <c r="H27" s="12">
         <v>17</v>
       </c>
@@ -1992,7 +2064,7 @@
       </c>
       <c r="K27" s="37"/>
       <c r="L27" s="37"/>
-      <c r="M27" s="15"/>
+      <c r="M27" s="37"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
@@ -2009,12 +2081,14 @@
       <c r="AA27" s="15"/>
       <c r="AB27" s="15"/>
       <c r="AC27" s="15"/>
-      <c r="AD27" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="8:30" ht="15.75">
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="8:32" ht="15.75">
       <c r="H28" s="12">
         <v>18</v>
       </c>
@@ -2026,7 +2100,7 @@
       </c>
       <c r="K28" s="37"/>
       <c r="L28" s="37"/>
-      <c r="M28" s="15"/>
+      <c r="M28" s="37"/>
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
@@ -2043,12 +2117,14 @@
       <c r="AA28" s="15"/>
       <c r="AB28" s="15"/>
       <c r="AC28" s="15"/>
-      <c r="AD28" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="8:30" ht="15.75">
+      <c r="AD28" s="15"/>
+      <c r="AE28" s="15"/>
+      <c r="AF28" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="8:32" ht="15.75">
       <c r="H29" s="12">
         <v>19</v>
       </c>
@@ -2060,12 +2136,12 @@
       </c>
       <c r="K29" s="37"/>
       <c r="L29" s="37"/>
-      <c r="M29" s="16"/>
+      <c r="M29" s="37"/>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
       <c r="P29" s="16"/>
       <c r="Q29" s="16"/>
-      <c r="R29" s="15"/>
+      <c r="R29" s="16"/>
       <c r="S29" s="15"/>
       <c r="T29" s="15"/>
       <c r="U29" s="15"/>
@@ -2077,12 +2153,14 @@
       <c r="AA29" s="15"/>
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
-      <c r="AD29" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="8:30" ht="15.75">
+      <c r="AD29" s="15"/>
+      <c r="AE29" s="15"/>
+      <c r="AF29" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="8:32" ht="15.75">
       <c r="H30" s="12">
         <v>20</v>
       </c>
@@ -2094,12 +2172,12 @@
       </c>
       <c r="K30" s="37"/>
       <c r="L30" s="37"/>
-      <c r="M30" s="16"/>
+      <c r="M30" s="37"/>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
       <c r="P30" s="16"/>
       <c r="Q30" s="16"/>
-      <c r="R30" s="15"/>
+      <c r="R30" s="16"/>
       <c r="S30" s="15"/>
       <c r="T30" s="15"/>
       <c r="U30" s="15"/>
@@ -2111,12 +2189,14 @@
       <c r="AA30" s="15"/>
       <c r="AB30" s="15"/>
       <c r="AC30" s="15"/>
-      <c r="AD30" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="8:30" ht="15.75">
+      <c r="AD30" s="15"/>
+      <c r="AE30" s="15"/>
+      <c r="AF30" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="8:32" ht="15.75">
       <c r="H31" s="12">
         <v>21</v>
       </c>
@@ -2128,7 +2208,7 @@
       </c>
       <c r="K31" s="37"/>
       <c r="L31" s="37"/>
-      <c r="M31" s="15"/>
+      <c r="M31" s="37"/>
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
       <c r="P31" s="15"/>
@@ -2145,12 +2225,14 @@
       <c r="AA31" s="15"/>
       <c r="AB31" s="15"/>
       <c r="AC31" s="15"/>
-      <c r="AD31" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="8:30" ht="15.75">
+      <c r="AD31" s="15"/>
+      <c r="AE31" s="15"/>
+      <c r="AF31" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="8:32" ht="15.75">
       <c r="H32" s="12">
         <v>22</v>
       </c>
@@ -2162,7 +2244,7 @@
       </c>
       <c r="K32" s="37"/>
       <c r="L32" s="37"/>
-      <c r="M32" s="15"/>
+      <c r="M32" s="37"/>
       <c r="N32" s="15"/>
       <c r="O32" s="15"/>
       <c r="P32" s="15"/>
@@ -2179,12 +2261,14 @@
       <c r="AA32" s="15"/>
       <c r="AB32" s="15"/>
       <c r="AC32" s="15"/>
-      <c r="AD32" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="8:30" ht="15.75">
+      <c r="AD32" s="15"/>
+      <c r="AE32" s="15"/>
+      <c r="AF32" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="8:32" ht="15.75">
       <c r="H33" s="12">
         <v>23</v>
       </c>
@@ -2196,12 +2280,12 @@
       </c>
       <c r="K33" s="37"/>
       <c r="L33" s="37"/>
-      <c r="M33" s="16"/>
+      <c r="M33" s="37"/>
       <c r="N33" s="16"/>
       <c r="O33" s="16"/>
       <c r="P33" s="16"/>
       <c r="Q33" s="16"/>
-      <c r="R33" s="15"/>
+      <c r="R33" s="16"/>
       <c r="S33" s="15"/>
       <c r="T33" s="15"/>
       <c r="U33" s="15"/>
@@ -2213,12 +2297,14 @@
       <c r="AA33" s="15"/>
       <c r="AB33" s="15"/>
       <c r="AC33" s="15"/>
-      <c r="AD33" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="8:30" ht="15.75">
+      <c r="AD33" s="15"/>
+      <c r="AE33" s="15"/>
+      <c r="AF33" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="8:32" ht="15.75">
       <c r="H34" s="12">
         <v>24</v>
       </c>
@@ -2230,12 +2316,12 @@
       </c>
       <c r="K34" s="37"/>
       <c r="L34" s="37"/>
-      <c r="M34" s="16"/>
+      <c r="M34" s="37"/>
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
-      <c r="R34" s="15"/>
+      <c r="R34" s="16"/>
       <c r="S34" s="15"/>
       <c r="T34" s="15"/>
       <c r="U34" s="15"/>
@@ -2247,12 +2333,14 @@
       <c r="AA34" s="15"/>
       <c r="AB34" s="15"/>
       <c r="AC34" s="15"/>
-      <c r="AD34" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="8:30" ht="15.75">
+      <c r="AD34" s="15"/>
+      <c r="AE34" s="15"/>
+      <c r="AF34" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="8:32" ht="15.75">
       <c r="H35" s="12">
         <v>25</v>
       </c>
@@ -2264,7 +2352,7 @@
       </c>
       <c r="K35" s="37"/>
       <c r="L35" s="37"/>
-      <c r="M35" s="15"/>
+      <c r="M35" s="37"/>
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
@@ -2281,12 +2369,14 @@
       <c r="AA35" s="15"/>
       <c r="AB35" s="15"/>
       <c r="AC35" s="15"/>
-      <c r="AD35" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="8:30" ht="15.75">
+      <c r="AD35" s="15"/>
+      <c r="AE35" s="15"/>
+      <c r="AF35" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="8:32" ht="15.75">
       <c r="H36" s="12">
         <v>26</v>
       </c>
@@ -2298,7 +2388,7 @@
       </c>
       <c r="K36" s="37"/>
       <c r="L36" s="37"/>
-      <c r="M36" s="15"/>
+      <c r="M36" s="37"/>
       <c r="N36" s="15"/>
       <c r="O36" s="15"/>
       <c r="P36" s="15"/>
@@ -2315,12 +2405,14 @@
       <c r="AA36" s="15"/>
       <c r="AB36" s="15"/>
       <c r="AC36" s="15"/>
-      <c r="AD36" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="8:30" ht="15.75">
+      <c r="AD36" s="15"/>
+      <c r="AE36" s="15"/>
+      <c r="AF36" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="8:32" ht="15.75">
       <c r="H37" s="12">
         <v>27</v>
       </c>
@@ -2332,12 +2424,12 @@
       </c>
       <c r="K37" s="37"/>
       <c r="L37" s="37"/>
-      <c r="M37" s="16"/>
+      <c r="M37" s="37"/>
       <c r="N37" s="16"/>
       <c r="O37" s="16"/>
       <c r="P37" s="16"/>
       <c r="Q37" s="16"/>
-      <c r="R37" s="15"/>
+      <c r="R37" s="16"/>
       <c r="S37" s="15"/>
       <c r="T37" s="15"/>
       <c r="U37" s="15"/>
@@ -2349,12 +2441,14 @@
       <c r="AA37" s="15"/>
       <c r="AB37" s="15"/>
       <c r="AC37" s="15"/>
-      <c r="AD37" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="8:30" ht="15.75">
+      <c r="AD37" s="15"/>
+      <c r="AE37" s="15"/>
+      <c r="AF37" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="8:32" ht="15.75">
       <c r="H38" s="12">
         <v>28</v>
       </c>
@@ -2366,12 +2460,12 @@
       </c>
       <c r="K38" s="37"/>
       <c r="L38" s="37"/>
-      <c r="M38" s="16"/>
+      <c r="M38" s="37"/>
       <c r="N38" s="16"/>
       <c r="O38" s="16"/>
       <c r="P38" s="16"/>
       <c r="Q38" s="16"/>
-      <c r="R38" s="15"/>
+      <c r="R38" s="16"/>
       <c r="S38" s="15"/>
       <c r="T38" s="15"/>
       <c r="U38" s="15"/>
@@ -2383,12 +2477,14 @@
       <c r="AA38" s="15"/>
       <c r="AB38" s="15"/>
       <c r="AC38" s="15"/>
-      <c r="AD38" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="8:30" ht="15.75">
+      <c r="AD38" s="15"/>
+      <c r="AE38" s="15"/>
+      <c r="AF38" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="8:32" ht="15.75">
       <c r="H39" s="12">
         <v>29</v>
       </c>
@@ -2400,7 +2496,7 @@
       </c>
       <c r="K39" s="37"/>
       <c r="L39" s="37"/>
-      <c r="M39" s="15"/>
+      <c r="M39" s="37"/>
       <c r="N39" s="15"/>
       <c r="O39" s="15"/>
       <c r="P39" s="15"/>
@@ -2417,12 +2513,14 @@
       <c r="AA39" s="15"/>
       <c r="AB39" s="15"/>
       <c r="AC39" s="15"/>
-      <c r="AD39" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="8:30" ht="15.75">
+      <c r="AD39" s="15"/>
+      <c r="AE39" s="15"/>
+      <c r="AF39" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="8:32" ht="15.75">
       <c r="H40" s="12">
         <v>30</v>
       </c>
@@ -2434,7 +2532,7 @@
       </c>
       <c r="K40" s="37"/>
       <c r="L40" s="37"/>
-      <c r="M40" s="15"/>
+      <c r="M40" s="37"/>
       <c r="N40" s="15"/>
       <c r="O40" s="15"/>
       <c r="P40" s="15"/>
@@ -2451,12 +2549,14 @@
       <c r="AA40" s="15"/>
       <c r="AB40" s="15"/>
       <c r="AC40" s="15"/>
-      <c r="AD40" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="8:30" ht="15.75">
+      <c r="AD40" s="15"/>
+      <c r="AE40" s="15"/>
+      <c r="AF40" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="8:32" ht="15.75">
       <c r="H41" s="12">
         <v>31</v>
       </c>
@@ -2468,12 +2568,12 @@
       </c>
       <c r="K41" s="37"/>
       <c r="L41" s="37"/>
-      <c r="M41" s="16"/>
+      <c r="M41" s="37"/>
       <c r="N41" s="16"/>
       <c r="O41" s="16"/>
       <c r="P41" s="16"/>
       <c r="Q41" s="16"/>
-      <c r="R41" s="15"/>
+      <c r="R41" s="16"/>
       <c r="S41" s="15"/>
       <c r="T41" s="15"/>
       <c r="U41" s="15"/>
@@ -2485,12 +2585,14 @@
       <c r="AA41" s="15"/>
       <c r="AB41" s="15"/>
       <c r="AC41" s="15"/>
-      <c r="AD41" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="8:30" ht="15.75">
+      <c r="AD41" s="15"/>
+      <c r="AE41" s="15"/>
+      <c r="AF41" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="8:32" ht="15.75">
       <c r="H42" s="46" t="s">
         <v>19</v>
       </c>
@@ -2498,39 +2600,36 @@
       <c r="J42" s="46"/>
       <c r="K42" s="21">
         <f>COUNTA(K11:K41)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="21">
-        <f t="shared" ref="L42:Z42" si="1">COUNTA(L11:L41)</f>
+        <f t="shared" ref="L42:AA42" si="1">COUNTA(L11:L41)</f>
+        <v>4</v>
+      </c>
+      <c r="M42" s="21"/>
+      <c r="N42" s="21">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="M42" s="21">
+      <c r="O42" s="21">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="N42" s="21">
+      <c r="P42" s="21">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Q42" s="21">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="R42" s="21">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O42" s="21">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="P42" s="21">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="Q42" s="21">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="R42" s="21">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
       <c r="S42" s="21">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="T42" s="21">
         <f t="shared" si="1"/>
@@ -2538,7 +2637,7 @@
       </c>
       <c r="U42" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="21">
         <f t="shared" si="1"/>
@@ -2546,7 +2645,7 @@
       </c>
       <c r="W42" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="21">
         <f t="shared" si="1"/>
@@ -2560,26 +2659,31 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="21"/>
+      <c r="AA42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="AB42" s="21"/>
       <c r="AC42" s="21"/>
-      <c r="AD42" s="17">
-        <f t="shared" ref="AD42" si="2">COUNTA(AD11:AD41)</f>
+      <c r="AD42" s="21"/>
+      <c r="AE42" s="21"/>
+      <c r="AF42" s="17">
+        <f t="shared" ref="AF42" si="2">COUNTA(AF11:AF41)</f>
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="H42:J42"/>
-    <mergeCell ref="H9:AD9"/>
+    <mergeCell ref="H9:AF9"/>
   </mergeCells>
-  <conditionalFormatting sqref="AD42">
-    <cfRule type="expression" dxfId="1" priority="10">
-      <formula>AM42="+"</formula>
+  <conditionalFormatting sqref="AF42">
+    <cfRule type="expression" dxfId="2" priority="10">
+      <formula>AO42="+"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11:AC41">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="K11:AE41">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Другое/study_chart_copy.xlsx
+++ b/Другое/study_chart_copy.xlsx
@@ -27,8 +27,73 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Собянин Евгений Андреевич (new)</author>
+  </authors>
+  <commentList>
+    <comment ref="AF21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Контроль 100%.
+Срыв был недавно, весь день был рядом с Аней, раздрожителей не было, в телефоне не сидел.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AF22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Контроль 100%.
+Срыв был недавно, весь день был рядом с Аней, раздрожителей не было, в телефоне не сидел.
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="35">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -130,6 +195,9 @@
   </si>
   <si>
     <t>Спорт (хотя бы одно упражнение)</t>
+  </si>
+  <si>
+    <t>Воздержание</t>
   </si>
 </sst>
 </file>
@@ -139,7 +207,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +295,21 @@
       <sz val="11"/>
       <color rgb="FF1C1917"/>
       <name val="Impact"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -570,14 +653,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA7FFA7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -1254,12 +1330,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1270,7 +1346,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H9:AF42"/>
+  <dimension ref="H9:AG42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="1"/>
@@ -1286,15 +1362,15 @@
     <col min="24" max="24" width="11.5703125" style="1" customWidth="1"/>
     <col min="25" max="25" width="14.5703125" style="1" customWidth="1"/>
     <col min="26" max="27" width="10" style="1" customWidth="1"/>
-    <col min="28" max="28" width="20.5703125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="28" style="1" customWidth="1"/>
     <col min="29" max="29" width="14.140625" style="1" customWidth="1"/>
     <col min="30" max="30" width="13.85546875" style="1" customWidth="1"/>
-    <col min="31" max="31" width="18.42578125" style="1" customWidth="1"/>
-    <col min="32" max="32" width="18" style="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="31" max="32" width="18.42578125" style="1" customWidth="1"/>
+    <col min="33" max="33" width="18" style="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:32" ht="45" customHeight="1">
+    <row r="9" spans="8:33" ht="45" customHeight="1">
       <c r="H9" s="47" t="s">
         <v>0</v>
       </c>
@@ -1322,8 +1398,9 @@
       <c r="AD9" s="48"/>
       <c r="AE9" s="48"/>
       <c r="AF9" s="48"/>
-    </row>
-    <row r="10" spans="8:32" ht="30" customHeight="1">
+      <c r="AG9" s="48"/>
+    </row>
+    <row r="10" spans="8:33" ht="30" customHeight="1">
       <c r="H10" s="10" t="s">
         <v>1</v>
       </c>
@@ -1396,11 +1473,14 @@
       <c r="AE10" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="AF10" s="26" t="s">
+      <c r="AF10" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG10" s="26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="8:32" ht="15.75">
+    <row r="11" spans="8:33" ht="15.75">
       <c r="H11" s="27">
         <v>1</v>
       </c>
@@ -1433,12 +1513,13 @@
       <c r="AC11" s="33"/>
       <c r="AD11" s="33"/>
       <c r="AE11" s="33"/>
-      <c r="AF11" s="36">
-        <f>COUNTA(K11:AE11)</f>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="36">
+        <f>COUNTA(K11:AF11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="8:32" ht="15.75">
+    <row r="12" spans="8:33" ht="15.75">
       <c r="H12" s="27">
         <v>2</v>
       </c>
@@ -1475,12 +1556,13 @@
       <c r="AE12" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="AF12" s="36">
-        <f t="shared" ref="AF12:AF41" si="0">COUNTA(K12:AE12)</f>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="36">
+        <f t="shared" ref="AG12:AG41" si="0">COUNTA(K12:AE12)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="8:32" ht="15.75">
+    <row r="13" spans="8:33" ht="15.75">
       <c r="H13" s="27">
         <v>3</v>
       </c>
@@ -1527,12 +1609,13 @@
       <c r="AC13" s="30"/>
       <c r="AD13" s="30"/>
       <c r="AE13" s="30"/>
-      <c r="AF13" s="36">
+      <c r="AF13" s="30"/>
+      <c r="AG13" s="36">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="8:32" ht="15.75">
+    <row r="14" spans="8:33" ht="15.75">
       <c r="H14" s="27">
         <v>4</v>
       </c>
@@ -1567,12 +1650,13 @@
       <c r="AC14" s="30"/>
       <c r="AD14" s="30"/>
       <c r="AE14" s="30"/>
-      <c r="AF14" s="36">
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="36">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="8:32" ht="15.75">
+    <row r="15" spans="8:33" ht="15.75">
       <c r="H15" s="27">
         <v>5</v>
       </c>
@@ -1609,12 +1693,13 @@
       <c r="AC15" s="30"/>
       <c r="AD15" s="30"/>
       <c r="AE15" s="30"/>
-      <c r="AF15" s="36">
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="36">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="8:32" ht="15.75">
+    <row r="16" spans="8:33" ht="15.75">
       <c r="H16" s="27">
         <v>6</v>
       </c>
@@ -1661,12 +1746,13 @@
       <c r="AE16" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="AF16" s="36">
+      <c r="AF16" s="30"/>
+      <c r="AG16" s="36">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="8:32" ht="15.75">
+    <row r="17" spans="8:33" ht="15.75">
       <c r="H17" s="27">
         <v>7</v>
       </c>
@@ -1711,226 +1797,270 @@
       <c r="AE17" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="AF17" s="36">
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="36">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="8:32" ht="15.75">
-      <c r="H18" s="12">
+    <row r="18" spans="8:33" ht="15.75">
+      <c r="H18" s="27">
         <v>8</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="29">
         <v>46211</v>
       </c>
-      <c r="K18" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="O18" s="16"/>
-      <c r="P18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="R18" s="16"/>
-      <c r="S18" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="T18" s="15"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="36">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="8:32" ht="15.75">
-      <c r="H19" s="12">
+      <c r="K18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="39"/>
+      <c r="N18" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" s="31"/>
+      <c r="P18" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="R18" s="31"/>
+      <c r="S18" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="X18" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="36">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="8:33" ht="15.75">
+      <c r="H19" s="27">
         <v>9</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="14">
+      <c r="J19" s="29">
         <v>46212</v>
       </c>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="15"/>
-      <c r="S19" s="15"/>
-      <c r="T19" s="15"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="15"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="15"/>
-      <c r="Y19" s="15"/>
-      <c r="Z19" s="15"/>
-      <c r="AA19" s="15"/>
-      <c r="AB19" s="15"/>
-      <c r="AC19" s="15"/>
-      <c r="AD19" s="15"/>
-      <c r="AE19" s="15"/>
-      <c r="AF19" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="8:32" ht="15.75">
-      <c r="H20" s="12">
+      <c r="K19" s="39"/>
+      <c r="L19" s="39"/>
+      <c r="M19" s="39"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="30"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="T19" s="30"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="30"/>
+      <c r="X19" s="30"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="30"/>
+      <c r="AA19" s="30"/>
+      <c r="AB19" s="30"/>
+      <c r="AC19" s="30"/>
+      <c r="AD19" s="30"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="8:33" ht="15.75">
+      <c r="H20" s="27">
         <v>10</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="I20" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="14">
+      <c r="J20" s="29">
         <v>46213</v>
       </c>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
-      <c r="AA20" s="15"/>
-      <c r="AB20" s="15"/>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="15"/>
-      <c r="AE20" s="15"/>
-      <c r="AF20" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="8:32" ht="15.75">
-      <c r="H21" s="12">
+      <c r="K20" s="39"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
+      <c r="AG20" s="36">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="8:33" ht="15.75">
+      <c r="H21" s="27">
         <v>11</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="I21" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J21" s="29">
         <v>46214</v>
       </c>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="15"/>
-      <c r="T21" s="15"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="15"/>
-      <c r="W21" s="15"/>
-      <c r="X21" s="15"/>
-      <c r="Y21" s="15"/>
-      <c r="Z21" s="15"/>
-      <c r="AA21" s="15"/>
-      <c r="AB21" s="15"/>
-      <c r="AC21" s="15"/>
-      <c r="AD21" s="15"/>
-      <c r="AE21" s="15"/>
-      <c r="AF21" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="8:32" ht="15.75">
-      <c r="H22" s="12">
-        <v>12</v>
-      </c>
-      <c r="I22" s="13" t="s">
+      <c r="K21" s="39"/>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="30"/>
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
+      <c r="AA21" s="30"/>
+      <c r="AB21" s="30"/>
+      <c r="AC21" s="30"/>
+      <c r="AD21" s="30"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG21" s="36">
+        <f>COUNTA(K21:AF21)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="8:33" ht="15.75">
+      <c r="H22" s="27">
+        <v>12</v>
+      </c>
+      <c r="I22" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="14">
+      <c r="J22" s="29">
         <v>46215</v>
       </c>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="15"/>
-      <c r="T22" s="15"/>
-      <c r="U22" s="15"/>
-      <c r="V22" s="15"/>
-      <c r="W22" s="15"/>
-      <c r="X22" s="15"/>
-      <c r="Y22" s="15"/>
-      <c r="Z22" s="15"/>
-      <c r="AA22" s="15"/>
-      <c r="AB22" s="15"/>
-      <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
-      <c r="AE22" s="15"/>
-      <c r="AF22" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="8:32" ht="15.75">
-      <c r="H23" s="12">
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="O22" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="P22" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q22" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="R22" s="31"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="30"/>
+      <c r="AB22" s="30"/>
+      <c r="AC22" s="30"/>
+      <c r="AD22" s="30"/>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG22" s="36">
+        <f>COUNTA(K22:AF22)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="8:33" ht="15.75">
+      <c r="H23" s="27">
         <v>13</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="J23" s="14">
+      <c r="J23" s="29">
         <v>46216</v>
       </c>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
+      <c r="K23" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="L23" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="N23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="R23" s="30"/>
+      <c r="S23" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
+      <c r="U23" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
+      <c r="W23" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="X23" s="15"/>
       <c r="Y23" s="15"/>
       <c r="Z23" s="15"/>
@@ -1939,12 +2069,13 @@
       <c r="AC23" s="15"/>
       <c r="AD23" s="15"/>
       <c r="AE23" s="15"/>
-      <c r="AF23" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="8:32" ht="15.75">
+      <c r="AF23" s="15"/>
+      <c r="AG23" s="36">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="8:33" ht="15.75">
       <c r="H24" s="12">
         <v>14</v>
       </c>
@@ -1975,12 +2106,13 @@
       <c r="AC24" s="15"/>
       <c r="AD24" s="15"/>
       <c r="AE24" s="15"/>
-      <c r="AF24" s="36">
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="8:32" ht="15.75">
+    <row r="25" spans="8:33" ht="15.75">
       <c r="H25" s="12">
         <v>15</v>
       </c>
@@ -2011,12 +2143,13 @@
       <c r="AC25" s="15"/>
       <c r="AD25" s="15"/>
       <c r="AE25" s="15"/>
-      <c r="AF25" s="36">
+      <c r="AF25" s="15"/>
+      <c r="AG25" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="8:32" ht="15.75">
+    <row r="26" spans="8:33" ht="15.75">
       <c r="H26" s="12">
         <v>16</v>
       </c>
@@ -2047,12 +2180,13 @@
       <c r="AC26" s="15"/>
       <c r="AD26" s="15"/>
       <c r="AE26" s="15"/>
-      <c r="AF26" s="36">
+      <c r="AF26" s="15"/>
+      <c r="AG26" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="8:32" ht="15.75">
+    <row r="27" spans="8:33" ht="15.75">
       <c r="H27" s="12">
         <v>17</v>
       </c>
@@ -2083,12 +2217,13 @@
       <c r="AC27" s="15"/>
       <c r="AD27" s="15"/>
       <c r="AE27" s="15"/>
-      <c r="AF27" s="36">
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="8:32" ht="15.75">
+    <row r="28" spans="8:33" ht="15.75">
       <c r="H28" s="12">
         <v>18</v>
       </c>
@@ -2119,12 +2254,13 @@
       <c r="AC28" s="15"/>
       <c r="AD28" s="15"/>
       <c r="AE28" s="15"/>
-      <c r="AF28" s="36">
+      <c r="AF28" s="15"/>
+      <c r="AG28" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="8:32" ht="15.75">
+    <row r="29" spans="8:33" ht="15.75">
       <c r="H29" s="12">
         <v>19</v>
       </c>
@@ -2155,12 +2291,13 @@
       <c r="AC29" s="15"/>
       <c r="AD29" s="15"/>
       <c r="AE29" s="15"/>
-      <c r="AF29" s="36">
+      <c r="AF29" s="15"/>
+      <c r="AG29" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="8:32" ht="15.75">
+    <row r="30" spans="8:33" ht="15.75">
       <c r="H30" s="12">
         <v>20</v>
       </c>
@@ -2191,12 +2328,13 @@
       <c r="AC30" s="15"/>
       <c r="AD30" s="15"/>
       <c r="AE30" s="15"/>
-      <c r="AF30" s="36">
+      <c r="AF30" s="15"/>
+      <c r="AG30" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="8:32" ht="15.75">
+    <row r="31" spans="8:33" ht="15.75">
       <c r="H31" s="12">
         <v>21</v>
       </c>
@@ -2227,12 +2365,13 @@
       <c r="AC31" s="15"/>
       <c r="AD31" s="15"/>
       <c r="AE31" s="15"/>
-      <c r="AF31" s="36">
+      <c r="AF31" s="15"/>
+      <c r="AG31" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="8:32" ht="15.75">
+    <row r="32" spans="8:33" ht="15.75">
       <c r="H32" s="12">
         <v>22</v>
       </c>
@@ -2263,12 +2402,13 @@
       <c r="AC32" s="15"/>
       <c r="AD32" s="15"/>
       <c r="AE32" s="15"/>
-      <c r="AF32" s="36">
+      <c r="AF32" s="15"/>
+      <c r="AG32" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="8:32" ht="15.75">
+    <row r="33" spans="8:33" ht="15.75">
       <c r="H33" s="12">
         <v>23</v>
       </c>
@@ -2299,12 +2439,13 @@
       <c r="AC33" s="15"/>
       <c r="AD33" s="15"/>
       <c r="AE33" s="15"/>
-      <c r="AF33" s="36">
+      <c r="AF33" s="15"/>
+      <c r="AG33" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="8:32" ht="15.75">
+    <row r="34" spans="8:33" ht="15.75">
       <c r="H34" s="12">
         <v>24</v>
       </c>
@@ -2335,12 +2476,13 @@
       <c r="AC34" s="15"/>
       <c r="AD34" s="15"/>
       <c r="AE34" s="15"/>
-      <c r="AF34" s="36">
+      <c r="AF34" s="15"/>
+      <c r="AG34" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="8:32" ht="15.75">
+    <row r="35" spans="8:33" ht="15.75">
       <c r="H35" s="12">
         <v>25</v>
       </c>
@@ -2371,12 +2513,13 @@
       <c r="AC35" s="15"/>
       <c r="AD35" s="15"/>
       <c r="AE35" s="15"/>
-      <c r="AF35" s="36">
+      <c r="AF35" s="15"/>
+      <c r="AG35" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="8:32" ht="15.75">
+    <row r="36" spans="8:33" ht="15.75">
       <c r="H36" s="12">
         <v>26</v>
       </c>
@@ -2407,12 +2550,13 @@
       <c r="AC36" s="15"/>
       <c r="AD36" s="15"/>
       <c r="AE36" s="15"/>
-      <c r="AF36" s="36">
+      <c r="AF36" s="15"/>
+      <c r="AG36" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="8:32" ht="15.75">
+    <row r="37" spans="8:33" ht="15.75">
       <c r="H37" s="12">
         <v>27</v>
       </c>
@@ -2443,12 +2587,13 @@
       <c r="AC37" s="15"/>
       <c r="AD37" s="15"/>
       <c r="AE37" s="15"/>
-      <c r="AF37" s="36">
+      <c r="AF37" s="15"/>
+      <c r="AG37" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="8:32" ht="15.75">
+    <row r="38" spans="8:33" ht="15.75">
       <c r="H38" s="12">
         <v>28</v>
       </c>
@@ -2479,12 +2624,13 @@
       <c r="AC38" s="15"/>
       <c r="AD38" s="15"/>
       <c r="AE38" s="15"/>
-      <c r="AF38" s="36">
+      <c r="AF38" s="15"/>
+      <c r="AG38" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="8:32" ht="15.75">
+    <row r="39" spans="8:33" ht="15.75">
       <c r="H39" s="12">
         <v>29</v>
       </c>
@@ -2515,12 +2661,13 @@
       <c r="AC39" s="15"/>
       <c r="AD39" s="15"/>
       <c r="AE39" s="15"/>
-      <c r="AF39" s="36">
+      <c r="AF39" s="15"/>
+      <c r="AG39" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="8:32" ht="15.75">
+    <row r="40" spans="8:33" ht="15.75">
       <c r="H40" s="12">
         <v>30</v>
       </c>
@@ -2551,12 +2698,13 @@
       <c r="AC40" s="15"/>
       <c r="AD40" s="15"/>
       <c r="AE40" s="15"/>
-      <c r="AF40" s="36">
+      <c r="AF40" s="15"/>
+      <c r="AG40" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="8:32" ht="15.75">
+    <row r="41" spans="8:33" ht="15.75">
       <c r="H41" s="12">
         <v>31</v>
       </c>
@@ -2587,12 +2735,13 @@
       <c r="AC41" s="15"/>
       <c r="AD41" s="15"/>
       <c r="AE41" s="15"/>
-      <c r="AF41" s="36">
+      <c r="AF41" s="15"/>
+      <c r="AG41" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="8:32" ht="15.75">
+    <row r="42" spans="8:33" ht="15.75">
       <c r="H42" s="46" t="s">
         <v>19</v>
       </c>
@@ -2600,28 +2749,28 @@
       <c r="J42" s="46"/>
       <c r="K42" s="21">
         <f>COUNTA(K11:K41)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="21">
         <f t="shared" ref="L42:AA42" si="1">COUNTA(L11:L41)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M42" s="21"/>
       <c r="N42" s="21">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O42" s="21">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" s="21">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q42" s="21">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R42" s="21">
         <f t="shared" si="1"/>
@@ -2629,7 +2778,7 @@
       </c>
       <c r="S42" s="21">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T42" s="21">
         <f t="shared" si="1"/>
@@ -2637,7 +2786,7 @@
       </c>
       <c r="U42" s="21">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V42" s="21">
         <f t="shared" si="1"/>
@@ -2645,11 +2794,11 @@
       </c>
       <c r="W42" s="21">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X42" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" s="21">
         <f t="shared" si="1"/>
@@ -2667,27 +2816,29 @@
       <c r="AC42" s="21"/>
       <c r="AD42" s="21"/>
       <c r="AE42" s="21"/>
-      <c r="AF42" s="17">
-        <f t="shared" ref="AF42" si="2">COUNTA(AF11:AF41)</f>
+      <c r="AF42" s="21"/>
+      <c r="AG42" s="17">
+        <f t="shared" ref="AG42" si="2">COUNTA(AG11:AG41)</f>
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="H42:J42"/>
-    <mergeCell ref="H9:AF9"/>
+    <mergeCell ref="H9:AG9"/>
   </mergeCells>
-  <conditionalFormatting sqref="AF42">
-    <cfRule type="expression" dxfId="2" priority="10">
-      <formula>AO42="+"</formula>
+  <conditionalFormatting sqref="AG42">
+    <cfRule type="expression" dxfId="1" priority="10">
+      <formula>AP42="+"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11:AE41">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="K11:AF41">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Другое/study_chart_copy.xlsx
+++ b/Другое/study_chart_copy.xlsx
@@ -88,12 +88,40 @@
         </r>
       </text>
     </comment>
+    <comment ref="AF23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Контроль уже не 100%,
+но мыслей о срыве не было.
+Упражнения, помогающие отогнать навязчивые мысли пока, что работают хорошо.
+Отсутствие телефона так же помогает
+сохранить концетрацию</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="35">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -207,7 +235,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,6 +339,27 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF680000"/>
+      <name val="Courier New"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -604,12 +653,6 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -648,6 +691,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -686,6 +735,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF680000"/>
       <color rgb="FFFF99CC"/>
       <color rgb="FFA7FFA7"/>
       <color rgb="FFB7FFB7"/>
@@ -695,7 +745,6 @@
       <color rgb="FF1B4965"/>
       <color rgb="FF4A3B32"/>
       <color rgb="FFF4EFEA"/>
-      <color rgb="FF3A2E2A"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1010,18 +1059,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="42"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="40"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="2" t="s">
@@ -1290,11 +1339,11 @@
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="43" t="s">
+      <c r="H22" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="44"/>
-      <c r="J22" s="45"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="43"/>
       <c r="K22" s="4">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -1371,34 +1420,34 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:33" ht="45" customHeight="1">
-      <c r="H9" s="47" t="s">
+      <c r="H9" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="48"/>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
-      <c r="M9" s="48"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="48"/>
-      <c r="P9" s="48"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="48"/>
-      <c r="S9" s="48"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="48"/>
-      <c r="V9" s="48"/>
-      <c r="W9" s="48"/>
-      <c r="X9" s="48"/>
-      <c r="Y9" s="48"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="48"/>
-      <c r="AB9" s="48"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="48"/>
-      <c r="AE9" s="48"/>
-      <c r="AF9" s="48"/>
-      <c r="AG9" s="48"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="46"/>
+      <c r="Y9" s="46"/>
+      <c r="Z9" s="46"/>
+      <c r="AA9" s="46"/>
+      <c r="AB9" s="46"/>
+      <c r="AC9" s="46"/>
+      <c r="AD9" s="46"/>
+      <c r="AE9" s="46"/>
+      <c r="AF9" s="46"/>
+      <c r="AG9" s="46"/>
     </row>
     <row r="10" spans="8:33" ht="30" customHeight="1">
       <c r="H10" s="10" t="s">
@@ -1461,19 +1510,19 @@
       <c r="AA10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="AB10" s="35" t="s">
+      <c r="AB10" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="AC10" s="34" t="s">
+      <c r="AC10" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="AD10" s="35" t="s">
+      <c r="AD10" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="AE10" s="35" t="s">
+      <c r="AE10" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="AF10" s="35" t="s">
+      <c r="AF10" s="47" t="s">
         <v>34</v>
       </c>
       <c r="AG10" s="26" t="s">
@@ -1514,7 +1563,7 @@
       <c r="AD11" s="33"/>
       <c r="AE11" s="33"/>
       <c r="AF11" s="33"/>
-      <c r="AG11" s="36">
+      <c r="AG11" s="34">
         <f>COUNTA(K11:AF11)</f>
         <v>1</v>
       </c>
@@ -1557,7 +1606,7 @@
         <v>12</v>
       </c>
       <c r="AF12" s="30"/>
-      <c r="AG12" s="36">
+      <c r="AG12" s="34">
         <f t="shared" ref="AG12:AG41" si="0">COUNTA(K12:AE12)</f>
         <v>3</v>
       </c>
@@ -1572,13 +1621,13 @@
       <c r="J13" s="29">
         <v>46206</v>
       </c>
-      <c r="K13" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="M13" s="38"/>
+      <c r="K13" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="36"/>
       <c r="N13" s="31" t="s">
         <v>12</v>
       </c>
@@ -1610,7 +1659,7 @@
       <c r="AD13" s="30"/>
       <c r="AE13" s="30"/>
       <c r="AF13" s="30"/>
-      <c r="AG13" s="36">
+      <c r="AG13" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1625,9 +1674,9 @@
       <c r="J14" s="29">
         <v>46207</v>
       </c>
-      <c r="K14" s="39"/>
-      <c r="L14" s="39"/>
-      <c r="M14" s="39"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="37"/>
       <c r="N14" s="31"/>
       <c r="O14" s="31"/>
       <c r="P14" s="31" t="s">
@@ -1651,7 +1700,7 @@
       <c r="AD14" s="30"/>
       <c r="AE14" s="30"/>
       <c r="AF14" s="30"/>
-      <c r="AG14" s="36">
+      <c r="AG14" s="34">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1666,9 +1715,9 @@
       <c r="J15" s="29">
         <v>46208</v>
       </c>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
       <c r="N15" s="30"/>
       <c r="O15" s="30" t="s">
         <v>12</v>
@@ -1694,7 +1743,7 @@
       <c r="AD15" s="30"/>
       <c r="AE15" s="30"/>
       <c r="AF15" s="30"/>
-      <c r="AG15" s="36">
+      <c r="AG15" s="34">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -1709,13 +1758,13 @@
       <c r="J16" s="29">
         <v>46209</v>
       </c>
-      <c r="K16" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="39"/>
+      <c r="K16" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" s="37"/>
       <c r="N16" s="30"/>
       <c r="O16" s="30"/>
       <c r="P16" s="30" t="s">
@@ -1747,7 +1796,7 @@
         <v>12</v>
       </c>
       <c r="AF16" s="30"/>
-      <c r="AG16" s="36">
+      <c r="AG16" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1762,11 +1811,11 @@
       <c r="J17" s="29">
         <v>46210</v>
       </c>
-      <c r="K17" s="39"/>
-      <c r="L17" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="39"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="37"/>
       <c r="N17" s="30" t="s">
         <v>12</v>
       </c>
@@ -1798,7 +1847,7 @@
         <v>12</v>
       </c>
       <c r="AF17" s="30"/>
-      <c r="AG17" s="36">
+      <c r="AG17" s="34">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -1813,13 +1862,13 @@
       <c r="J18" s="29">
         <v>46211</v>
       </c>
-      <c r="K18" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="M18" s="39"/>
+      <c r="K18" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="37"/>
       <c r="N18" s="30" t="s">
         <v>12</v>
       </c>
@@ -1851,7 +1900,7 @@
       <c r="AD18" s="30"/>
       <c r="AE18" s="30"/>
       <c r="AF18" s="30"/>
-      <c r="AG18" s="36">
+      <c r="AG18" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -1866,9 +1915,9 @@
       <c r="J19" s="29">
         <v>46212</v>
       </c>
-      <c r="K19" s="39"/>
-      <c r="L19" s="39"/>
-      <c r="M19" s="39"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
       <c r="N19" s="30"/>
       <c r="O19" s="30"/>
       <c r="P19" s="30"/>
@@ -1890,7 +1939,7 @@
       <c r="AD19" s="30"/>
       <c r="AE19" s="30"/>
       <c r="AF19" s="30"/>
-      <c r="AG19" s="36">
+      <c r="AG19" s="34">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1905,9 +1954,9 @@
       <c r="J20" s="29">
         <v>46213</v>
       </c>
-      <c r="K20" s="39"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="39"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="37"/>
       <c r="N20" s="30"/>
       <c r="O20" s="30"/>
       <c r="P20" s="30"/>
@@ -1929,7 +1978,7 @@
       <c r="AD20" s="30"/>
       <c r="AE20" s="30"/>
       <c r="AF20" s="30"/>
-      <c r="AG20" s="36">
+      <c r="AG20" s="34">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -1944,9 +1993,9 @@
       <c r="J21" s="29">
         <v>46214</v>
       </c>
-      <c r="K21" s="39"/>
-      <c r="L21" s="39"/>
-      <c r="M21" s="39"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
       <c r="N21" s="31"/>
       <c r="O21" s="31"/>
       <c r="P21" s="31"/>
@@ -1968,7 +2017,7 @@
       <c r="AF21" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AG21" s="36">
+      <c r="AG21" s="34">
         <f>COUNTA(K21:AF21)</f>
         <v>1</v>
       </c>
@@ -1983,9 +2032,9 @@
       <c r="J22" s="29">
         <v>46215</v>
       </c>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
+      <c r="M22" s="37"/>
       <c r="N22" s="30" t="s">
         <v>12</v>
       </c>
@@ -2015,7 +2064,7 @@
       <c r="AF22" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="AG22" s="36">
+      <c r="AG22" s="34">
         <f>COUNTA(K22:AF22)</f>
         <v>5</v>
       </c>
@@ -2030,13 +2079,13 @@
       <c r="J23" s="29">
         <v>46216</v>
       </c>
-      <c r="K23" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" s="39" t="s">
-        <v>12</v>
-      </c>
-      <c r="M23" s="39" t="s">
+      <c r="K23" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="L23" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>12</v>
       </c>
       <c r="N23" s="30" t="s">
@@ -2050,29 +2099,37 @@
         <v>12</v>
       </c>
       <c r="R23" s="30"/>
-      <c r="S23" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="X23" s="15"/>
-      <c r="Y23" s="15"/>
-      <c r="Z23" s="15"/>
-      <c r="AA23" s="15"/>
-      <c r="AB23" s="15"/>
-      <c r="AC23" s="15"/>
-      <c r="AD23" s="15"/>
-      <c r="AE23" s="15"/>
-      <c r="AF23" s="15"/>
-      <c r="AG23" s="36">
-        <f t="shared" si="0"/>
-        <v>9</v>
+      <c r="S23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="30"/>
+      <c r="AB23" s="30"/>
+      <c r="AC23" s="30"/>
+      <c r="AD23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF23" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG23" s="34">
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="8:33" ht="15.75">
@@ -2085,13 +2142,21 @@
       <c r="J24" s="14">
         <v>46217</v>
       </c>
-      <c r="K24" s="37"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="15"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="N24" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="15"/>
+      <c r="P24" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="R24" s="15"/>
       <c r="S24" s="15"/>
       <c r="T24" s="15"/>
@@ -2107,9 +2172,9 @@
       <c r="AD24" s="15"/>
       <c r="AE24" s="15"/>
       <c r="AF24" s="15"/>
-      <c r="AG24" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="AG24" s="34">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="8:33" ht="15.75">
@@ -2122,9 +2187,9 @@
       <c r="J25" s="14">
         <v>46218</v>
       </c>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="37"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
       <c r="N25" s="16"/>
       <c r="O25" s="16"/>
       <c r="P25" s="16"/>
@@ -2144,7 +2209,7 @@
       <c r="AD25" s="15"/>
       <c r="AE25" s="15"/>
       <c r="AF25" s="15"/>
-      <c r="AG25" s="36">
+      <c r="AG25" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2159,9 +2224,9 @@
       <c r="J26" s="14">
         <v>46219</v>
       </c>
-      <c r="K26" s="37"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="37"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
       <c r="N26" s="16"/>
       <c r="O26" s="16"/>
       <c r="P26" s="16"/>
@@ -2181,7 +2246,7 @@
       <c r="AD26" s="15"/>
       <c r="AE26" s="15"/>
       <c r="AF26" s="15"/>
-      <c r="AG26" s="36">
+      <c r="AG26" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2196,9 +2261,9 @@
       <c r="J27" s="14">
         <v>46220</v>
       </c>
-      <c r="K27" s="37"/>
-      <c r="L27" s="37"/>
-      <c r="M27" s="37"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
@@ -2218,7 +2283,7 @@
       <c r="AD27" s="15"/>
       <c r="AE27" s="15"/>
       <c r="AF27" s="15"/>
-      <c r="AG27" s="36">
+      <c r="AG27" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2233,9 +2298,9 @@
       <c r="J28" s="14">
         <v>46221</v>
       </c>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
@@ -2255,7 +2320,7 @@
       <c r="AD28" s="15"/>
       <c r="AE28" s="15"/>
       <c r="AF28" s="15"/>
-      <c r="AG28" s="36">
+      <c r="AG28" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2270,9 +2335,9 @@
       <c r="J29" s="14">
         <v>46222</v>
       </c>
-      <c r="K29" s="37"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="37"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
       <c r="P29" s="16"/>
@@ -2292,7 +2357,7 @@
       <c r="AD29" s="15"/>
       <c r="AE29" s="15"/>
       <c r="AF29" s="15"/>
-      <c r="AG29" s="36">
+      <c r="AG29" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2307,9 +2372,9 @@
       <c r="J30" s="14">
         <v>46223</v>
       </c>
-      <c r="K30" s="37"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="37"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
       <c r="P30" s="16"/>
@@ -2329,7 +2394,7 @@
       <c r="AD30" s="15"/>
       <c r="AE30" s="15"/>
       <c r="AF30" s="15"/>
-      <c r="AG30" s="36">
+      <c r="AG30" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2344,9 +2409,9 @@
       <c r="J31" s="14">
         <v>46224</v>
       </c>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
       <c r="P31" s="15"/>
@@ -2366,7 +2431,7 @@
       <c r="AD31" s="15"/>
       <c r="AE31" s="15"/>
       <c r="AF31" s="15"/>
-      <c r="AG31" s="36">
+      <c r="AG31" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2381,9 +2446,9 @@
       <c r="J32" s="14">
         <v>46225</v>
       </c>
-      <c r="K32" s="37"/>
-      <c r="L32" s="37"/>
-      <c r="M32" s="37"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
       <c r="N32" s="15"/>
       <c r="O32" s="15"/>
       <c r="P32" s="15"/>
@@ -2403,7 +2468,7 @@
       <c r="AD32" s="15"/>
       <c r="AE32" s="15"/>
       <c r="AF32" s="15"/>
-      <c r="AG32" s="36">
+      <c r="AG32" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2418,9 +2483,9 @@
       <c r="J33" s="14">
         <v>46226</v>
       </c>
-      <c r="K33" s="37"/>
-      <c r="L33" s="37"/>
-      <c r="M33" s="37"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
       <c r="N33" s="16"/>
       <c r="O33" s="16"/>
       <c r="P33" s="16"/>
@@ -2440,7 +2505,7 @@
       <c r="AD33" s="15"/>
       <c r="AE33" s="15"/>
       <c r="AF33" s="15"/>
-      <c r="AG33" s="36">
+      <c r="AG33" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2455,9 +2520,9 @@
       <c r="J34" s="14">
         <v>46227</v>
       </c>
-      <c r="K34" s="37"/>
-      <c r="L34" s="37"/>
-      <c r="M34" s="37"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
       <c r="P34" s="16"/>
@@ -2477,7 +2542,7 @@
       <c r="AD34" s="15"/>
       <c r="AE34" s="15"/>
       <c r="AF34" s="15"/>
-      <c r="AG34" s="36">
+      <c r="AG34" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2492,9 +2557,9 @@
       <c r="J35" s="14">
         <v>46228</v>
       </c>
-      <c r="K35" s="37"/>
-      <c r="L35" s="37"/>
-      <c r="M35" s="37"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
@@ -2514,7 +2579,7 @@
       <c r="AD35" s="15"/>
       <c r="AE35" s="15"/>
       <c r="AF35" s="15"/>
-      <c r="AG35" s="36">
+      <c r="AG35" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2529,9 +2594,9 @@
       <c r="J36" s="14">
         <v>46229</v>
       </c>
-      <c r="K36" s="37"/>
-      <c r="L36" s="37"/>
-      <c r="M36" s="37"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
       <c r="N36" s="15"/>
       <c r="O36" s="15"/>
       <c r="P36" s="15"/>
@@ -2551,7 +2616,7 @@
       <c r="AD36" s="15"/>
       <c r="AE36" s="15"/>
       <c r="AF36" s="15"/>
-      <c r="AG36" s="36">
+      <c r="AG36" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2566,9 +2631,9 @@
       <c r="J37" s="14">
         <v>46230</v>
       </c>
-      <c r="K37" s="37"/>
-      <c r="L37" s="37"/>
-      <c r="M37" s="37"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="35"/>
       <c r="N37" s="16"/>
       <c r="O37" s="16"/>
       <c r="P37" s="16"/>
@@ -2588,7 +2653,7 @@
       <c r="AD37" s="15"/>
       <c r="AE37" s="15"/>
       <c r="AF37" s="15"/>
-      <c r="AG37" s="36">
+      <c r="AG37" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2603,9 +2668,9 @@
       <c r="J38" s="14">
         <v>46231</v>
       </c>
-      <c r="K38" s="37"/>
-      <c r="L38" s="37"/>
-      <c r="M38" s="37"/>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="35"/>
       <c r="N38" s="16"/>
       <c r="O38" s="16"/>
       <c r="P38" s="16"/>
@@ -2625,7 +2690,7 @@
       <c r="AD38" s="15"/>
       <c r="AE38" s="15"/>
       <c r="AF38" s="15"/>
-      <c r="AG38" s="36">
+      <c r="AG38" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2640,9 +2705,9 @@
       <c r="J39" s="14">
         <v>46232</v>
       </c>
-      <c r="K39" s="37"/>
-      <c r="L39" s="37"/>
-      <c r="M39" s="37"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="35"/>
       <c r="N39" s="15"/>
       <c r="O39" s="15"/>
       <c r="P39" s="15"/>
@@ -2662,7 +2727,7 @@
       <c r="AD39" s="15"/>
       <c r="AE39" s="15"/>
       <c r="AF39" s="15"/>
-      <c r="AG39" s="36">
+      <c r="AG39" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2677,9 +2742,9 @@
       <c r="J40" s="14">
         <v>46233</v>
       </c>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37"/>
-      <c r="M40" s="37"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35"/>
       <c r="N40" s="15"/>
       <c r="O40" s="15"/>
       <c r="P40" s="15"/>
@@ -2699,7 +2764,7 @@
       <c r="AD40" s="15"/>
       <c r="AE40" s="15"/>
       <c r="AF40" s="15"/>
-      <c r="AG40" s="36">
+      <c r="AG40" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2714,9 +2779,9 @@
       <c r="J41" s="14">
         <v>46234</v>
       </c>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37"/>
-      <c r="M41" s="37"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
       <c r="N41" s="16"/>
       <c r="O41" s="16"/>
       <c r="P41" s="16"/>
@@ -2736,29 +2801,32 @@
       <c r="AD41" s="15"/>
       <c r="AE41" s="15"/>
       <c r="AF41" s="15"/>
-      <c r="AG41" s="36">
+      <c r="AG41" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="8:33" ht="15.75">
-      <c r="H42" s="46" t="s">
+      <c r="H42" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
       <c r="K42" s="21">
         <f>COUNTA(K11:K41)</f>
         <v>4</v>
       </c>
       <c r="L42" s="21">
-        <f t="shared" ref="L42:AA42" si="1">COUNTA(L11:L41)</f>
+        <f t="shared" ref="L42:AF42" si="1">COUNTA(L11:L41)</f>
         <v>5</v>
       </c>
-      <c r="M42" s="21"/>
+      <c r="M42" s="21">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
       <c r="N42" s="21">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O42" s="21">
         <f t="shared" si="1"/>
@@ -2766,11 +2834,11 @@
       </c>
       <c r="P42" s="21">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q42" s="21">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R42" s="21">
         <f t="shared" si="1"/>
@@ -2802,7 +2870,7 @@
       </c>
       <c r="Y42" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="21">
         <f t="shared" si="1"/>
@@ -2812,11 +2880,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB42" s="21"/>
-      <c r="AC42" s="21"/>
-      <c r="AD42" s="21"/>
-      <c r="AE42" s="21"/>
-      <c r="AF42" s="21"/>
+      <c r="AB42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AC42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AD42" s="21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AE42" s="21">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AF42" s="21">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
       <c r="AG42" s="17">
         <f t="shared" ref="AG42" si="2">COUNTA(AG11:AG41)</f>
         <v>31</v>

--- a/Другое/study_chart_copy.xlsx
+++ b/Другое/study_chart_copy.xlsx
@@ -116,12 +116,60 @@
         </r>
       </text>
     </comment>
+    <comment ref="AG24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Найти квартиру для поездки в МСК</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AH24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Определиться с подарком Кулику</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="36">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -226,6 +274,9 @@
   </si>
   <si>
     <t>Воздержание</t>
+  </si>
+  <si>
+    <t>Доп.задание</t>
   </si>
 </sst>
 </file>
@@ -235,7 +286,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,8 +413,16 @@
       <family val="3"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFF4EFEA"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -433,6 +492,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -665,6 +730,15 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -691,12 +765,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -735,6 +803,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF4EFEA"/>
       <color rgb="FF680000"/>
       <color rgb="FFFF99CC"/>
       <color rgb="FFA7FFA7"/>
@@ -744,7 +813,6 @@
       <color rgb="FFC1292E"/>
       <color rgb="FF1B4965"/>
       <color rgb="FF4A3B32"/>
-      <color rgb="FFF4EFEA"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1059,18 +1127,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="38" t="s">
+      <c r="H9" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="40"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="43"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="2" t="s">
@@ -1339,11 +1407,11 @@
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="41" t="s">
+      <c r="H22" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="43"/>
+      <c r="I22" s="45"/>
+      <c r="J22" s="46"/>
       <c r="K22" s="4">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -1395,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H9:AG42"/>
+  <dimension ref="H9:AJ42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="1"/>
@@ -1414,42 +1482,45 @@
     <col min="28" max="28" width="28" style="1" customWidth="1"/>
     <col min="29" max="29" width="14.140625" style="1" customWidth="1"/>
     <col min="30" max="30" width="13.85546875" style="1" customWidth="1"/>
-    <col min="31" max="32" width="18.42578125" style="1" customWidth="1"/>
-    <col min="33" max="33" width="18" style="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="31" max="35" width="18.42578125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="18" style="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:33" ht="45" customHeight="1">
-      <c r="H9" s="45" t="s">
+    <row r="9" spans="8:36" ht="45" customHeight="1">
+      <c r="H9" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="46"/>
-      <c r="Y9" s="46"/>
-      <c r="Z9" s="46"/>
-      <c r="AA9" s="46"/>
-      <c r="AB9" s="46"/>
-      <c r="AC9" s="46"/>
-      <c r="AD9" s="46"/>
-      <c r="AE9" s="46"/>
-      <c r="AF9" s="46"/>
-      <c r="AG9" s="46"/>
-    </row>
-    <row r="10" spans="8:33" ht="30" customHeight="1">
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="49"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="49"/>
+      <c r="AA9" s="49"/>
+      <c r="AB9" s="49"/>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="49"/>
+      <c r="AE9" s="49"/>
+      <c r="AF9" s="49"/>
+      <c r="AG9" s="49"/>
+      <c r="AH9" s="49"/>
+      <c r="AI9" s="49"/>
+      <c r="AJ9" s="49"/>
+    </row>
+    <row r="10" spans="8:36" ht="30" customHeight="1">
       <c r="H10" s="10" t="s">
         <v>1</v>
       </c>
@@ -1510,26 +1581,35 @@
       <c r="AA10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="AB10" s="47" t="s">
+      <c r="AB10" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="AC10" s="48" t="s">
+      <c r="AC10" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AD10" s="47" t="s">
+      <c r="AD10" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="AE10" s="47" t="s">
+      <c r="AE10" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="AF10" s="47" t="s">
+      <c r="AF10" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AG10" s="26" t="s">
+      <c r="AG10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ10" s="26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="8:33" ht="15.75">
+    <row r="11" spans="8:36" ht="15.75">
       <c r="H11" s="27">
         <v>1</v>
       </c>
@@ -1563,12 +1643,15 @@
       <c r="AD11" s="33"/>
       <c r="AE11" s="33"/>
       <c r="AF11" s="33"/>
-      <c r="AG11" s="34">
-        <f>COUNTA(K11:AF11)</f>
+      <c r="AG11" s="33"/>
+      <c r="AH11" s="33"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="34">
+        <f>COUNTA(K11:AI11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="8:33" ht="15.75">
+    <row r="12" spans="8:36" ht="15.75">
       <c r="H12" s="27">
         <v>2</v>
       </c>
@@ -1606,12 +1689,15 @@
         <v>12</v>
       </c>
       <c r="AF12" s="30"/>
-      <c r="AG12" s="34">
-        <f t="shared" ref="AG12:AG41" si="0">COUNTA(K12:AE12)</f>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="30"/>
+      <c r="AJ12" s="34">
+        <f t="shared" ref="AJ12:AJ41" si="0">COUNTA(K12:AI12)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="8:33" ht="15.75">
+    <row r="13" spans="8:36" ht="15.75">
       <c r="H13" s="27">
         <v>3</v>
       </c>
@@ -1659,12 +1745,15 @@
       <c r="AD13" s="30"/>
       <c r="AE13" s="30"/>
       <c r="AF13" s="30"/>
-      <c r="AG13" s="34">
+      <c r="AG13" s="30"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="30"/>
+      <c r="AJ13" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="8:33" ht="15.75">
+    <row r="14" spans="8:36" ht="15.75">
       <c r="H14" s="27">
         <v>4</v>
       </c>
@@ -1700,12 +1789,15 @@
       <c r="AD14" s="30"/>
       <c r="AE14" s="30"/>
       <c r="AF14" s="30"/>
-      <c r="AG14" s="34">
+      <c r="AG14" s="30"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="34">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="8:33" ht="15.75">
+    <row r="15" spans="8:36" ht="15.75">
       <c r="H15" s="27">
         <v>5</v>
       </c>
@@ -1743,12 +1835,15 @@
       <c r="AD15" s="30"/>
       <c r="AE15" s="30"/>
       <c r="AF15" s="30"/>
-      <c r="AG15" s="34">
+      <c r="AG15" s="30"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="30"/>
+      <c r="AJ15" s="34">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="8:33" ht="15.75">
+    <row r="16" spans="8:36" ht="15.75">
       <c r="H16" s="27">
         <v>6</v>
       </c>
@@ -1796,12 +1891,15 @@
         <v>12</v>
       </c>
       <c r="AF16" s="30"/>
-      <c r="AG16" s="34">
+      <c r="AG16" s="30"/>
+      <c r="AH16" s="30"/>
+      <c r="AI16" s="30"/>
+      <c r="AJ16" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="8:33" ht="15.75">
+    <row r="17" spans="8:36" ht="15.75">
       <c r="H17" s="27">
         <v>7</v>
       </c>
@@ -1847,12 +1945,15 @@
         <v>12</v>
       </c>
       <c r="AF17" s="30"/>
-      <c r="AG17" s="34">
+      <c r="AG17" s="30"/>
+      <c r="AH17" s="30"/>
+      <c r="AI17" s="30"/>
+      <c r="AJ17" s="34">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="8:33" ht="15.75">
+    <row r="18" spans="8:36" ht="15.75">
       <c r="H18" s="27">
         <v>8</v>
       </c>
@@ -1900,12 +2001,15 @@
       <c r="AD18" s="30"/>
       <c r="AE18" s="30"/>
       <c r="AF18" s="30"/>
-      <c r="AG18" s="34">
+      <c r="AG18" s="30"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="30"/>
+      <c r="AJ18" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="8:33" ht="15.75">
+    <row r="19" spans="8:36" ht="15.75">
       <c r="H19" s="27">
         <v>9</v>
       </c>
@@ -1939,12 +2043,15 @@
       <c r="AD19" s="30"/>
       <c r="AE19" s="30"/>
       <c r="AF19" s="30"/>
-      <c r="AG19" s="34">
+      <c r="AG19" s="30"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="30"/>
+      <c r="AJ19" s="34">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="8:33" ht="15.75">
+    <row r="20" spans="8:36" ht="15.75">
       <c r="H20" s="27">
         <v>10</v>
       </c>
@@ -1978,12 +2085,15 @@
       <c r="AD20" s="30"/>
       <c r="AE20" s="30"/>
       <c r="AF20" s="30"/>
-      <c r="AG20" s="34">
+      <c r="AG20" s="30"/>
+      <c r="AH20" s="30"/>
+      <c r="AI20" s="30"/>
+      <c r="AJ20" s="34">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="8:33" ht="15.75">
+    <row r="21" spans="8:36" ht="15.75">
       <c r="H21" s="27">
         <v>11</v>
       </c>
@@ -2017,12 +2127,15 @@
       <c r="AF21" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="AG21" s="34">
-        <f>COUNTA(K21:AF21)</f>
+      <c r="AG21" s="30"/>
+      <c r="AH21" s="30"/>
+      <c r="AI21" s="30"/>
+      <c r="AJ21" s="34">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="8:33" ht="15.75">
+    <row r="22" spans="8:36" ht="15.75">
       <c r="H22" s="27">
         <v>12</v>
       </c>
@@ -2064,12 +2177,15 @@
       <c r="AF22" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="AG22" s="34">
-        <f>COUNTA(K22:AF22)</f>
+      <c r="AG22" s="30"/>
+      <c r="AH22" s="30"/>
+      <c r="AI22" s="30"/>
+      <c r="AJ22" s="34">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="8:33" ht="15.75">
+    <row r="23" spans="8:36" ht="15.75">
       <c r="H23" s="27">
         <v>13</v>
       </c>
@@ -2127,39 +2243,46 @@
       <c r="AF23" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="AG23" s="34">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="8:33" ht="15.75">
-      <c r="H24" s="12">
+      <c r="AG23" s="30"/>
+      <c r="AH23" s="30"/>
+      <c r="AI23" s="30"/>
+      <c r="AJ23" s="34">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="8:36" ht="15.75">
+      <c r="H24" s="27">
         <v>14</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I24" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="14">
+      <c r="J24" s="29">
         <v>46217</v>
       </c>
-      <c r="K24" s="35"/>
-      <c r="L24" s="35"/>
-      <c r="M24" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="N24" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q24" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="R24" s="15"/>
-      <c r="S24" s="15"/>
-      <c r="T24" s="15"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
+      <c r="M24" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="N24" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="R24" s="30"/>
+      <c r="S24" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="T24" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="U24" s="15"/>
       <c r="V24" s="15"/>
       <c r="W24" s="15"/>
@@ -2172,12 +2295,15 @@
       <c r="AD24" s="15"/>
       <c r="AE24" s="15"/>
       <c r="AF24" s="15"/>
-      <c r="AG24" s="34">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="8:33" ht="15.75">
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="15"/>
+      <c r="AI24" s="15"/>
+      <c r="AJ24" s="34">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="8:36" ht="15.75">
       <c r="H25" s="12">
         <v>15</v>
       </c>
@@ -2209,12 +2335,15 @@
       <c r="AD25" s="15"/>
       <c r="AE25" s="15"/>
       <c r="AF25" s="15"/>
-      <c r="AG25" s="34">
+      <c r="AG25" s="15"/>
+      <c r="AH25" s="15"/>
+      <c r="AI25" s="15"/>
+      <c r="AJ25" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="8:33" ht="15.75">
+    <row r="26" spans="8:36" ht="15.75">
       <c r="H26" s="12">
         <v>16</v>
       </c>
@@ -2246,12 +2375,15 @@
       <c r="AD26" s="15"/>
       <c r="AE26" s="15"/>
       <c r="AF26" s="15"/>
-      <c r="AG26" s="34">
+      <c r="AG26" s="15"/>
+      <c r="AH26" s="15"/>
+      <c r="AI26" s="15"/>
+      <c r="AJ26" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="8:33" ht="15.75">
+    <row r="27" spans="8:36" ht="15.75">
       <c r="H27" s="12">
         <v>17</v>
       </c>
@@ -2283,12 +2415,15 @@
       <c r="AD27" s="15"/>
       <c r="AE27" s="15"/>
       <c r="AF27" s="15"/>
-      <c r="AG27" s="34">
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="15"/>
+      <c r="AI27" s="15"/>
+      <c r="AJ27" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="8:33" ht="15.75">
+    <row r="28" spans="8:36" ht="15.75">
       <c r="H28" s="12">
         <v>18</v>
       </c>
@@ -2320,12 +2455,15 @@
       <c r="AD28" s="15"/>
       <c r="AE28" s="15"/>
       <c r="AF28" s="15"/>
-      <c r="AG28" s="34">
+      <c r="AG28" s="15"/>
+      <c r="AH28" s="15"/>
+      <c r="AI28" s="15"/>
+      <c r="AJ28" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="8:33" ht="15.75">
+    <row r="29" spans="8:36" ht="15.75">
       <c r="H29" s="12">
         <v>19</v>
       </c>
@@ -2357,12 +2495,15 @@
       <c r="AD29" s="15"/>
       <c r="AE29" s="15"/>
       <c r="AF29" s="15"/>
-      <c r="AG29" s="34">
+      <c r="AG29" s="15"/>
+      <c r="AH29" s="15"/>
+      <c r="AI29" s="15"/>
+      <c r="AJ29" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="8:33" ht="15.75">
+    <row r="30" spans="8:36" ht="15.75">
       <c r="H30" s="12">
         <v>20</v>
       </c>
@@ -2394,12 +2535,15 @@
       <c r="AD30" s="15"/>
       <c r="AE30" s="15"/>
       <c r="AF30" s="15"/>
-      <c r="AG30" s="34">
+      <c r="AG30" s="15"/>
+      <c r="AH30" s="15"/>
+      <c r="AI30" s="15"/>
+      <c r="AJ30" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="8:33" ht="15.75">
+    <row r="31" spans="8:36" ht="15.75">
       <c r="H31" s="12">
         <v>21</v>
       </c>
@@ -2431,12 +2575,15 @@
       <c r="AD31" s="15"/>
       <c r="AE31" s="15"/>
       <c r="AF31" s="15"/>
-      <c r="AG31" s="34">
+      <c r="AG31" s="15"/>
+      <c r="AH31" s="15"/>
+      <c r="AI31" s="15"/>
+      <c r="AJ31" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="8:33" ht="15.75">
+    <row r="32" spans="8:36" ht="15.75">
       <c r="H32" s="12">
         <v>22</v>
       </c>
@@ -2468,12 +2615,15 @@
       <c r="AD32" s="15"/>
       <c r="AE32" s="15"/>
       <c r="AF32" s="15"/>
-      <c r="AG32" s="34">
+      <c r="AG32" s="15"/>
+      <c r="AH32" s="15"/>
+      <c r="AI32" s="15"/>
+      <c r="AJ32" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="8:33" ht="15.75">
+    <row r="33" spans="8:36" ht="15.75">
       <c r="H33" s="12">
         <v>23</v>
       </c>
@@ -2505,12 +2655,15 @@
       <c r="AD33" s="15"/>
       <c r="AE33" s="15"/>
       <c r="AF33" s="15"/>
-      <c r="AG33" s="34">
+      <c r="AG33" s="15"/>
+      <c r="AH33" s="15"/>
+      <c r="AI33" s="15"/>
+      <c r="AJ33" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="8:33" ht="15.75">
+    <row r="34" spans="8:36" ht="15.75">
       <c r="H34" s="12">
         <v>24</v>
       </c>
@@ -2542,12 +2695,15 @@
       <c r="AD34" s="15"/>
       <c r="AE34" s="15"/>
       <c r="AF34" s="15"/>
-      <c r="AG34" s="34">
+      <c r="AG34" s="15"/>
+      <c r="AH34" s="15"/>
+      <c r="AI34" s="15"/>
+      <c r="AJ34" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="8:33" ht="15.75">
+    <row r="35" spans="8:36" ht="15.75">
       <c r="H35" s="12">
         <v>25</v>
       </c>
@@ -2579,12 +2735,15 @@
       <c r="AD35" s="15"/>
       <c r="AE35" s="15"/>
       <c r="AF35" s="15"/>
-      <c r="AG35" s="34">
+      <c r="AG35" s="15"/>
+      <c r="AH35" s="15"/>
+      <c r="AI35" s="15"/>
+      <c r="AJ35" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="8:33" ht="15.75">
+    <row r="36" spans="8:36" ht="15.75">
       <c r="H36" s="12">
         <v>26</v>
       </c>
@@ -2616,12 +2775,15 @@
       <c r="AD36" s="15"/>
       <c r="AE36" s="15"/>
       <c r="AF36" s="15"/>
-      <c r="AG36" s="34">
+      <c r="AG36" s="15"/>
+      <c r="AH36" s="15"/>
+      <c r="AI36" s="15"/>
+      <c r="AJ36" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="8:33" ht="15.75">
+    <row r="37" spans="8:36" ht="15.75">
       <c r="H37" s="12">
         <v>27</v>
       </c>
@@ -2653,12 +2815,15 @@
       <c r="AD37" s="15"/>
       <c r="AE37" s="15"/>
       <c r="AF37" s="15"/>
-      <c r="AG37" s="34">
+      <c r="AG37" s="15"/>
+      <c r="AH37" s="15"/>
+      <c r="AI37" s="15"/>
+      <c r="AJ37" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="8:33" ht="15.75">
+    <row r="38" spans="8:36" ht="15.75">
       <c r="H38" s="12">
         <v>28</v>
       </c>
@@ -2690,12 +2855,15 @@
       <c r="AD38" s="15"/>
       <c r="AE38" s="15"/>
       <c r="AF38" s="15"/>
-      <c r="AG38" s="34">
+      <c r="AG38" s="15"/>
+      <c r="AH38" s="15"/>
+      <c r="AI38" s="15"/>
+      <c r="AJ38" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="8:33" ht="15.75">
+    <row r="39" spans="8:36" ht="15.75">
       <c r="H39" s="12">
         <v>29</v>
       </c>
@@ -2727,12 +2895,15 @@
       <c r="AD39" s="15"/>
       <c r="AE39" s="15"/>
       <c r="AF39" s="15"/>
-      <c r="AG39" s="34">
+      <c r="AG39" s="15"/>
+      <c r="AH39" s="15"/>
+      <c r="AI39" s="15"/>
+      <c r="AJ39" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="8:33" ht="15.75">
+    <row r="40" spans="8:36" ht="15.75">
       <c r="H40" s="12">
         <v>30</v>
       </c>
@@ -2764,12 +2935,15 @@
       <c r="AD40" s="15"/>
       <c r="AE40" s="15"/>
       <c r="AF40" s="15"/>
-      <c r="AG40" s="34">
+      <c r="AG40" s="15"/>
+      <c r="AH40" s="15"/>
+      <c r="AI40" s="15"/>
+      <c r="AJ40" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="8:33" ht="15.75">
+    <row r="41" spans="8:36" ht="15.75">
       <c r="H41" s="12">
         <v>31</v>
       </c>
@@ -2801,23 +2975,26 @@
       <c r="AD41" s="15"/>
       <c r="AE41" s="15"/>
       <c r="AF41" s="15"/>
-      <c r="AG41" s="34">
+      <c r="AG41" s="15"/>
+      <c r="AH41" s="15"/>
+      <c r="AI41" s="15"/>
+      <c r="AJ41" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="8:33" ht="15.75">
-      <c r="H42" s="44" t="s">
+    <row r="42" spans="8:36" ht="15.75">
+      <c r="H42" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47"/>
       <c r="K42" s="21">
         <f>COUNTA(K11:K41)</f>
         <v>4</v>
       </c>
       <c r="L42" s="21">
-        <f t="shared" ref="L42:AF42" si="1">COUNTA(L11:L41)</f>
+        <f t="shared" ref="L42:AI42" si="1">COUNTA(L11:L41)</f>
         <v>5</v>
       </c>
       <c r="M42" s="21">
@@ -2846,11 +3023,11 @@
       </c>
       <c r="S42" s="21">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" s="21">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U42" s="21">
         <f t="shared" si="1"/>
@@ -2900,22 +3077,34 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="AG42" s="17">
-        <f t="shared" ref="AG42" si="2">COUNTA(AG11:AG41)</f>
+      <c r="AG42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="17">
+        <f t="shared" ref="AJ42" si="2">COUNTA(AJ11:AJ41)</f>
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="H42:J42"/>
-    <mergeCell ref="H9:AG9"/>
+    <mergeCell ref="H9:AJ9"/>
   </mergeCells>
-  <conditionalFormatting sqref="AG42">
+  <conditionalFormatting sqref="AJ42">
     <cfRule type="expression" dxfId="1" priority="10">
-      <formula>AP42="+"</formula>
+      <formula>AS42="+"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11:AF41">
+  <conditionalFormatting sqref="K11:AI41">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>

--- a/Другое/study_chart_copy.xlsx
+++ b/Другое/study_chart_copy.xlsx
@@ -116,6 +116,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="AF24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Контроль 80%
+Уже чувствуется напряжение, но мыслей о том чтобы сорваться не было
+Уже начинаются разные триггеры, которые не должны по идее меня беспокоить.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AG24" authorId="0">
       <text>
         <r>
@@ -164,12 +190,137 @@
         </r>
       </text>
     </comment>
+    <comment ref="AG25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Найти квартиру для поездки в МСК</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AH25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Определиться с подарком Кулику</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AI25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Разобраться с заявлением</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AJ25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Определиться с одеждой в мск</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AK25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Собянин Евгений Андреевич (new):
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Сходить в парикмахерскую</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="36">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1463,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H9:AJ42"/>
+  <dimension ref="H9:AL42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="1"/>
@@ -1482,12 +1633,12 @@
     <col min="28" max="28" width="28" style="1" customWidth="1"/>
     <col min="29" max="29" width="14.140625" style="1" customWidth="1"/>
     <col min="30" max="30" width="13.85546875" style="1" customWidth="1"/>
-    <col min="31" max="35" width="18.42578125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="18" style="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="31" max="37" width="18.42578125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="18" style="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:36" ht="45" customHeight="1">
+    <row r="9" spans="8:38" ht="45" customHeight="1">
       <c r="H9" s="48" t="s">
         <v>0</v>
       </c>
@@ -1519,8 +1670,10 @@
       <c r="AH9" s="49"/>
       <c r="AI9" s="49"/>
       <c r="AJ9" s="49"/>
-    </row>
-    <row r="10" spans="8:36" ht="30" customHeight="1">
+      <c r="AK9" s="49"/>
+      <c r="AL9" s="49"/>
+    </row>
+    <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="10" t="s">
         <v>1</v>
       </c>
@@ -1605,11 +1758,17 @@
       <c r="AI10" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="AJ10" s="26" t="s">
+      <c r="AJ10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL10" s="26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="8:36" ht="15.75">
+    <row r="11" spans="8:38" ht="15.75">
       <c r="H11" s="27">
         <v>1</v>
       </c>
@@ -1646,12 +1805,14 @@
       <c r="AG11" s="33"/>
       <c r="AH11" s="33"/>
       <c r="AI11" s="33"/>
-      <c r="AJ11" s="34">
-        <f>COUNTA(K11:AI11)</f>
+      <c r="AJ11" s="33"/>
+      <c r="AK11" s="33"/>
+      <c r="AL11" s="34">
+        <f>COUNTA(K11:AK11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="8:36" ht="15.75">
+    <row r="12" spans="8:38" ht="15.75">
       <c r="H12" s="27">
         <v>2</v>
       </c>
@@ -1692,12 +1853,14 @@
       <c r="AG12" s="30"/>
       <c r="AH12" s="30"/>
       <c r="AI12" s="30"/>
-      <c r="AJ12" s="34">
-        <f t="shared" ref="AJ12:AJ41" si="0">COUNTA(K12:AI12)</f>
+      <c r="AJ12" s="30"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="34">
+        <f t="shared" ref="AL12:AL41" si="0">COUNTA(K12:AK12)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="8:36" ht="15.75">
+    <row r="13" spans="8:38" ht="15.75">
       <c r="H13" s="27">
         <v>3</v>
       </c>
@@ -1748,12 +1911,14 @@
       <c r="AG13" s="30"/>
       <c r="AH13" s="30"/>
       <c r="AI13" s="30"/>
-      <c r="AJ13" s="34">
+      <c r="AJ13" s="30"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="8:36" ht="15.75">
+    <row r="14" spans="8:38" ht="15.75">
       <c r="H14" s="27">
         <v>4</v>
       </c>
@@ -1792,12 +1957,14 @@
       <c r="AG14" s="30"/>
       <c r="AH14" s="30"/>
       <c r="AI14" s="30"/>
-      <c r="AJ14" s="34">
+      <c r="AJ14" s="30"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="34">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="8:36" ht="15.75">
+    <row r="15" spans="8:38" ht="15.75">
       <c r="H15" s="27">
         <v>5</v>
       </c>
@@ -1838,12 +2005,14 @@
       <c r="AG15" s="30"/>
       <c r="AH15" s="30"/>
       <c r="AI15" s="30"/>
-      <c r="AJ15" s="34">
+      <c r="AJ15" s="30"/>
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="34">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="8:36" ht="15.75">
+    <row r="16" spans="8:38" ht="15.75">
       <c r="H16" s="27">
         <v>6</v>
       </c>
@@ -1894,12 +2063,14 @@
       <c r="AG16" s="30"/>
       <c r="AH16" s="30"/>
       <c r="AI16" s="30"/>
-      <c r="AJ16" s="34">
+      <c r="AJ16" s="30"/>
+      <c r="AK16" s="30"/>
+      <c r="AL16" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="8:36" ht="15.75">
+    <row r="17" spans="8:38" ht="15.75">
       <c r="H17" s="27">
         <v>7</v>
       </c>
@@ -1948,12 +2119,14 @@
       <c r="AG17" s="30"/>
       <c r="AH17" s="30"/>
       <c r="AI17" s="30"/>
-      <c r="AJ17" s="34">
+      <c r="AJ17" s="30"/>
+      <c r="AK17" s="30"/>
+      <c r="AL17" s="34">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="8:36" ht="15.75">
+    <row r="18" spans="8:38" ht="15.75">
       <c r="H18" s="27">
         <v>8</v>
       </c>
@@ -2004,12 +2177,14 @@
       <c r="AG18" s="30"/>
       <c r="AH18" s="30"/>
       <c r="AI18" s="30"/>
-      <c r="AJ18" s="34">
+      <c r="AJ18" s="30"/>
+      <c r="AK18" s="30"/>
+      <c r="AL18" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="8:36" ht="15.75">
+    <row r="19" spans="8:38" ht="15.75">
       <c r="H19" s="27">
         <v>9</v>
       </c>
@@ -2046,12 +2221,14 @@
       <c r="AG19" s="30"/>
       <c r="AH19" s="30"/>
       <c r="AI19" s="30"/>
-      <c r="AJ19" s="34">
+      <c r="AJ19" s="30"/>
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="34">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="8:36" ht="15.75">
+    <row r="20" spans="8:38" ht="15.75">
       <c r="H20" s="27">
         <v>10</v>
       </c>
@@ -2088,12 +2265,14 @@
       <c r="AG20" s="30"/>
       <c r="AH20" s="30"/>
       <c r="AI20" s="30"/>
-      <c r="AJ20" s="34">
+      <c r="AJ20" s="30"/>
+      <c r="AK20" s="30"/>
+      <c r="AL20" s="34">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="8:36" ht="15.75">
+    <row r="21" spans="8:38" ht="15.75">
       <c r="H21" s="27">
         <v>11</v>
       </c>
@@ -2130,12 +2309,14 @@
       <c r="AG21" s="30"/>
       <c r="AH21" s="30"/>
       <c r="AI21" s="30"/>
-      <c r="AJ21" s="34">
+      <c r="AJ21" s="30"/>
+      <c r="AK21" s="30"/>
+      <c r="AL21" s="34">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="8:36" ht="15.75">
+    <row r="22" spans="8:38" ht="15.75">
       <c r="H22" s="27">
         <v>12</v>
       </c>
@@ -2180,12 +2361,14 @@
       <c r="AG22" s="30"/>
       <c r="AH22" s="30"/>
       <c r="AI22" s="30"/>
-      <c r="AJ22" s="34">
+      <c r="AJ22" s="30"/>
+      <c r="AK22" s="30"/>
+      <c r="AL22" s="34">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="8:36" ht="15.75">
+    <row r="23" spans="8:38" ht="15.75">
       <c r="H23" s="27">
         <v>13</v>
       </c>
@@ -2246,12 +2429,14 @@
       <c r="AG23" s="30"/>
       <c r="AH23" s="30"/>
       <c r="AI23" s="30"/>
-      <c r="AJ23" s="34">
+      <c r="AJ23" s="30"/>
+      <c r="AK23" s="30"/>
+      <c r="AL23" s="34">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="8:36" ht="15.75">
+    <row r="24" spans="8:38" ht="15.75">
       <c r="H24" s="27">
         <v>14</v>
       </c>
@@ -2283,67 +2468,83 @@
       <c r="T24" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="U24" s="15"/>
-      <c r="V24" s="15"/>
-      <c r="W24" s="15"/>
-      <c r="X24" s="15"/>
-      <c r="Y24" s="15"/>
-      <c r="Z24" s="15"/>
-      <c r="AA24" s="15"/>
-      <c r="AB24" s="15"/>
-      <c r="AC24" s="15"/>
-      <c r="AD24" s="15"/>
-      <c r="AE24" s="15"/>
-      <c r="AF24" s="15"/>
-      <c r="AG24" s="15"/>
-      <c r="AH24" s="15"/>
-      <c r="AI24" s="15"/>
-      <c r="AJ24" s="34">
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG24" s="30"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="34">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="8:36" ht="15.75">
-      <c r="H25" s="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="8:38" ht="15.75">
+      <c r="H25" s="27">
         <v>15</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I25" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J25" s="14">
+      <c r="J25" s="29">
         <v>46218</v>
       </c>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
-      <c r="AI25" s="15"/>
-      <c r="AJ25" s="34">
+      <c r="K25" s="37"/>
+      <c r="L25" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q25" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="R25" s="31"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="30"/>
+      <c r="X25" s="30"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="30"/>
+      <c r="AA25" s="30"/>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="30"/>
+      <c r="AD25" s="30"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="30"/>
+      <c r="AG25" s="30"/>
+      <c r="AH25" s="30"/>
+      <c r="AI25" s="30"/>
+      <c r="AJ25" s="30"/>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="8:36" ht="15.75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="8:38" ht="15.75">
       <c r="H26" s="12">
         <v>16</v>
       </c>
@@ -2378,12 +2579,14 @@
       <c r="AG26" s="15"/>
       <c r="AH26" s="15"/>
       <c r="AI26" s="15"/>
-      <c r="AJ26" s="34">
+      <c r="AJ26" s="15"/>
+      <c r="AK26" s="15"/>
+      <c r="AL26" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="8:36" ht="15.75">
+    <row r="27" spans="8:38" ht="15.75">
       <c r="H27" s="12">
         <v>17</v>
       </c>
@@ -2418,12 +2621,14 @@
       <c r="AG27" s="15"/>
       <c r="AH27" s="15"/>
       <c r="AI27" s="15"/>
-      <c r="AJ27" s="34">
+      <c r="AJ27" s="15"/>
+      <c r="AK27" s="15"/>
+      <c r="AL27" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="8:36" ht="15.75">
+    <row r="28" spans="8:38" ht="15.75">
       <c r="H28" s="12">
         <v>18</v>
       </c>
@@ -2458,12 +2663,14 @@
       <c r="AG28" s="15"/>
       <c r="AH28" s="15"/>
       <c r="AI28" s="15"/>
-      <c r="AJ28" s="34">
+      <c r="AJ28" s="15"/>
+      <c r="AK28" s="15"/>
+      <c r="AL28" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="8:36" ht="15.75">
+    <row r="29" spans="8:38" ht="15.75">
       <c r="H29" s="12">
         <v>19</v>
       </c>
@@ -2498,12 +2705,14 @@
       <c r="AG29" s="15"/>
       <c r="AH29" s="15"/>
       <c r="AI29" s="15"/>
-      <c r="AJ29" s="34">
+      <c r="AJ29" s="15"/>
+      <c r="AK29" s="15"/>
+      <c r="AL29" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="8:36" ht="15.75">
+    <row r="30" spans="8:38" ht="15.75">
       <c r="H30" s="12">
         <v>20</v>
       </c>
@@ -2538,12 +2747,14 @@
       <c r="AG30" s="15"/>
       <c r="AH30" s="15"/>
       <c r="AI30" s="15"/>
-      <c r="AJ30" s="34">
+      <c r="AJ30" s="15"/>
+      <c r="AK30" s="15"/>
+      <c r="AL30" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="8:36" ht="15.75">
+    <row r="31" spans="8:38" ht="15.75">
       <c r="H31" s="12">
         <v>21</v>
       </c>
@@ -2578,12 +2789,14 @@
       <c r="AG31" s="15"/>
       <c r="AH31" s="15"/>
       <c r="AI31" s="15"/>
-      <c r="AJ31" s="34">
+      <c r="AJ31" s="15"/>
+      <c r="AK31" s="15"/>
+      <c r="AL31" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="8:36" ht="15.75">
+    <row r="32" spans="8:38" ht="15.75">
       <c r="H32" s="12">
         <v>22</v>
       </c>
@@ -2618,12 +2831,14 @@
       <c r="AG32" s="15"/>
       <c r="AH32" s="15"/>
       <c r="AI32" s="15"/>
-      <c r="AJ32" s="34">
+      <c r="AJ32" s="15"/>
+      <c r="AK32" s="15"/>
+      <c r="AL32" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="8:36" ht="15.75">
+    <row r="33" spans="8:38" ht="15.75">
       <c r="H33" s="12">
         <v>23</v>
       </c>
@@ -2658,12 +2873,14 @@
       <c r="AG33" s="15"/>
       <c r="AH33" s="15"/>
       <c r="AI33" s="15"/>
-      <c r="AJ33" s="34">
+      <c r="AJ33" s="15"/>
+      <c r="AK33" s="15"/>
+      <c r="AL33" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="8:36" ht="15.75">
+    <row r="34" spans="8:38" ht="15.75">
       <c r="H34" s="12">
         <v>24</v>
       </c>
@@ -2698,12 +2915,14 @@
       <c r="AG34" s="15"/>
       <c r="AH34" s="15"/>
       <c r="AI34" s="15"/>
-      <c r="AJ34" s="34">
+      <c r="AJ34" s="15"/>
+      <c r="AK34" s="15"/>
+      <c r="AL34" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="8:36" ht="15.75">
+    <row r="35" spans="8:38" ht="15.75">
       <c r="H35" s="12">
         <v>25</v>
       </c>
@@ -2738,12 +2957,14 @@
       <c r="AG35" s="15"/>
       <c r="AH35" s="15"/>
       <c r="AI35" s="15"/>
-      <c r="AJ35" s="34">
+      <c r="AJ35" s="15"/>
+      <c r="AK35" s="15"/>
+      <c r="AL35" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="8:36" ht="15.75">
+    <row r="36" spans="8:38" ht="15.75">
       <c r="H36" s="12">
         <v>26</v>
       </c>
@@ -2778,12 +2999,14 @@
       <c r="AG36" s="15"/>
       <c r="AH36" s="15"/>
       <c r="AI36" s="15"/>
-      <c r="AJ36" s="34">
+      <c r="AJ36" s="15"/>
+      <c r="AK36" s="15"/>
+      <c r="AL36" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="8:36" ht="15.75">
+    <row r="37" spans="8:38" ht="15.75">
       <c r="H37" s="12">
         <v>27</v>
       </c>
@@ -2818,12 +3041,14 @@
       <c r="AG37" s="15"/>
       <c r="AH37" s="15"/>
       <c r="AI37" s="15"/>
-      <c r="AJ37" s="34">
+      <c r="AJ37" s="15"/>
+      <c r="AK37" s="15"/>
+      <c r="AL37" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="8:36" ht="15.75">
+    <row r="38" spans="8:38" ht="15.75">
       <c r="H38" s="12">
         <v>28</v>
       </c>
@@ -2858,12 +3083,14 @@
       <c r="AG38" s="15"/>
       <c r="AH38" s="15"/>
       <c r="AI38" s="15"/>
-      <c r="AJ38" s="34">
+      <c r="AJ38" s="15"/>
+      <c r="AK38" s="15"/>
+      <c r="AL38" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="8:36" ht="15.75">
+    <row r="39" spans="8:38" ht="15.75">
       <c r="H39" s="12">
         <v>29</v>
       </c>
@@ -2898,12 +3125,14 @@
       <c r="AG39" s="15"/>
       <c r="AH39" s="15"/>
       <c r="AI39" s="15"/>
-      <c r="AJ39" s="34">
+      <c r="AJ39" s="15"/>
+      <c r="AK39" s="15"/>
+      <c r="AL39" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="8:36" ht="15.75">
+    <row r="40" spans="8:38" ht="15.75">
       <c r="H40" s="12">
         <v>30</v>
       </c>
@@ -2938,12 +3167,14 @@
       <c r="AG40" s="15"/>
       <c r="AH40" s="15"/>
       <c r="AI40" s="15"/>
-      <c r="AJ40" s="34">
+      <c r="AJ40" s="15"/>
+      <c r="AK40" s="15"/>
+      <c r="AL40" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="8:36" ht="15.75">
+    <row r="41" spans="8:38" ht="15.75">
       <c r="H41" s="12">
         <v>31</v>
       </c>
@@ -2978,12 +3209,14 @@
       <c r="AG41" s="15"/>
       <c r="AH41" s="15"/>
       <c r="AI41" s="15"/>
-      <c r="AJ41" s="34">
+      <c r="AJ41" s="15"/>
+      <c r="AK41" s="15"/>
+      <c r="AL41" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="8:36" ht="15.75">
+    <row r="42" spans="8:38" ht="15.75">
       <c r="H42" s="47" t="s">
         <v>19</v>
       </c>
@@ -2994,12 +3227,12 @@
         <v>4</v>
       </c>
       <c r="L42" s="21">
-        <f t="shared" ref="L42:AI42" si="1">COUNTA(L11:L41)</f>
-        <v>5</v>
+        <f t="shared" ref="L42:AK42" si="1">COUNTA(L11:L41)</f>
+        <v>6</v>
       </c>
       <c r="M42" s="21">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N42" s="21">
         <f t="shared" si="1"/>
@@ -3011,11 +3244,11 @@
       </c>
       <c r="P42" s="21">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q42" s="21">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R42" s="21">
         <f t="shared" si="1"/>
@@ -3039,7 +3272,7 @@
       </c>
       <c r="W42" s="21">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X42" s="21">
         <f t="shared" si="1"/>
@@ -3075,7 +3308,7 @@
       </c>
       <c r="AF42" s="21">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG42" s="21">
         <f t="shared" si="1"/>
@@ -3085,26 +3318,28 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AI42" s="21">
+      <c r="AI42" s="21"/>
+      <c r="AJ42" s="21"/>
+      <c r="AK42" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AJ42" s="17">
-        <f t="shared" ref="AJ42" si="2">COUNTA(AJ11:AJ41)</f>
+      <c r="AL42" s="17">
+        <f t="shared" ref="AL42" si="2">COUNTA(AL11:AL41)</f>
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="H42:J42"/>
-    <mergeCell ref="H9:AJ9"/>
+    <mergeCell ref="H9:AL9"/>
   </mergeCells>
-  <conditionalFormatting sqref="AJ42">
+  <conditionalFormatting sqref="AL42">
     <cfRule type="expression" dxfId="1" priority="10">
-      <formula>AS42="+"</formula>
+      <formula>AU42="+"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K11:AI41">
+  <conditionalFormatting sqref="K11:AK41">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>

--- a/Другое/study_chart_copy.xlsx
+++ b/Другое/study_chart_copy.xlsx
@@ -190,6 +190,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="AF25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Контроль 80%
+Происходит треш (Аня чудит),
+возбуждение приходит быстро,
+но мыслей сорваться до сих пор
+нет, держу свои мысли под контролем - полет нормальный.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AG25" authorId="0">
       <text>
         <r>
@@ -311,7 +339,7 @@
             <family val="2"/>
             <charset val="204"/>
           </rPr>
-          <t>Сходить в парикмахерскую</t>
+          <t>Записаться в парикмахерскую</t>
         </r>
       </text>
     </comment>
@@ -320,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="36">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -2520,11 +2548,17 @@
         <v>12</v>
       </c>
       <c r="R25" s="31"/>
-      <c r="S25" s="30"/>
-      <c r="T25" s="30"/>
+      <c r="S25" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="T25" s="30" t="s">
+        <v>12</v>
+      </c>
       <c r="U25" s="30"/>
       <c r="V25" s="30"/>
-      <c r="W25" s="30"/>
+      <c r="W25" s="30" t="s">
+        <v>12</v>
+      </c>
       <c r="X25" s="30"/>
       <c r="Y25" s="30"/>
       <c r="Z25" s="30"/>
@@ -2533,15 +2567,19 @@
       <c r="AC25" s="30"/>
       <c r="AD25" s="30"/>
       <c r="AE25" s="30"/>
-      <c r="AF25" s="30"/>
+      <c r="AF25" s="30" t="s">
+        <v>12</v>
+      </c>
       <c r="AG25" s="30"/>
       <c r="AH25" s="30"/>
       <c r="AI25" s="30"/>
       <c r="AJ25" s="30"/>
-      <c r="AK25" s="30"/>
+      <c r="AK25" s="30" t="s">
+        <v>12</v>
+      </c>
       <c r="AL25" s="34">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="8:38" ht="15.75">
@@ -3256,11 +3294,11 @@
       </c>
       <c r="S42" s="21">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" s="21">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U42" s="21">
         <f t="shared" si="1"/>
@@ -3272,7 +3310,7 @@
       </c>
       <c r="W42" s="21">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X42" s="21">
         <f t="shared" si="1"/>
@@ -3308,7 +3346,7 @@
       </c>
       <c r="AF42" s="21">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG42" s="21">
         <f t="shared" si="1"/>
@@ -3322,7 +3360,7 @@
       <c r="AJ42" s="21"/>
       <c r="AK42" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL42" s="17">
         <f t="shared" ref="AL42" si="2">COUNTA(AL11:AL41)</f>

--- a/Другое/study_chart_copy.xlsx
+++ b/Другое/study_chart_copy.xlsx
@@ -343,12 +343,160 @@
         </r>
       </text>
     </comment>
+    <comment ref="AF26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AG26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Найти квартиру для поездки в МСК</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AH26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Определиться с подарком Кулику</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AI26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Разобраться с заявлением</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AJ26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Определиться с одеждой в мск</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AK26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Собянин Евгений Андреевич (new):</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Сходить в парикмахерскую</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="36">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -601,7 +749,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -677,6 +825,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -810,7 +964,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -944,6 +1098,20 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2583,45 +2751,55 @@
       </c>
     </row>
     <row r="26" spans="8:38" ht="15.75">
-      <c r="H26" s="12">
+      <c r="H26" s="50">
         <v>16</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="I26" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="14">
+      <c r="J26" s="52">
         <v>46219</v>
       </c>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="15"/>
-      <c r="W26" s="15"/>
-      <c r="X26" s="15"/>
-      <c r="Y26" s="15"/>
-      <c r="Z26" s="15"/>
-      <c r="AA26" s="15"/>
-      <c r="AB26" s="15"/>
-      <c r="AC26" s="15"/>
-      <c r="AD26" s="15"/>
-      <c r="AE26" s="15"/>
-      <c r="AF26" s="15"/>
-      <c r="AG26" s="15"/>
-      <c r="AH26" s="15"/>
-      <c r="AI26" s="15"/>
-      <c r="AJ26" s="15"/>
-      <c r="AK26" s="15"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="53"/>
+      <c r="M26" s="53" t="s">
+        <v>12</v>
+      </c>
+      <c r="N26" s="54"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
+      <c r="R26" s="54"/>
+      <c r="S26" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="T26" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="U26" s="55"/>
+      <c r="V26" s="55"/>
+      <c r="W26" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="X26" s="55"/>
+      <c r="Y26" s="55"/>
+      <c r="Z26" s="55"/>
+      <c r="AA26" s="55"/>
+      <c r="AB26" s="55"/>
+      <c r="AC26" s="55"/>
+      <c r="AD26" s="55"/>
+      <c r="AE26" s="55"/>
+      <c r="AF26" s="55"/>
+      <c r="AG26" s="55"/>
+      <c r="AH26" s="55"/>
+      <c r="AI26" s="55"/>
+      <c r="AJ26" s="55"/>
+      <c r="AK26" s="55" t="s">
+        <v>12</v>
+      </c>
       <c r="AL26" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="8:38" ht="15.75">
@@ -3270,7 +3448,7 @@
       </c>
       <c r="M42" s="21">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" s="21">
         <f t="shared" si="1"/>
@@ -3294,11 +3472,11 @@
       </c>
       <c r="S42" s="21">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T42" s="21">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U42" s="21">
         <f t="shared" si="1"/>
@@ -3310,7 +3488,7 @@
       </c>
       <c r="W42" s="21">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X42" s="21">
         <f t="shared" si="1"/>
@@ -3360,7 +3538,7 @@
       <c r="AJ42" s="21"/>
       <c r="AK42" s="21">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL42" s="17">
         <f t="shared" ref="AL42" si="2">COUNTA(AL11:AL41)</f>

--- a/Другое/study_chart_copy.xlsx
+++ b/Другое/study_chart_copy.xlsx
@@ -496,7 +496,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="36">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -749,7 +749,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -825,12 +825,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -964,7 +958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1098,20 +1092,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2751,55 +2731,61 @@
       </c>
     </row>
     <row r="26" spans="8:38" ht="15.75">
-      <c r="H26" s="50">
+      <c r="H26" s="27">
         <v>16</v>
       </c>
-      <c r="I26" s="51" t="s">
+      <c r="I26" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="52">
+      <c r="J26" s="29">
         <v>46219</v>
       </c>
-      <c r="K26" s="53"/>
-      <c r="L26" s="53"/>
-      <c r="M26" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="N26" s="54"/>
-      <c r="O26" s="54"/>
-      <c r="P26" s="54"/>
-      <c r="Q26" s="54"/>
-      <c r="R26" s="54"/>
-      <c r="S26" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="T26" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="U26" s="55"/>
-      <c r="V26" s="55"/>
-      <c r="W26" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="X26" s="55"/>
-      <c r="Y26" s="55"/>
-      <c r="Z26" s="55"/>
-      <c r="AA26" s="55"/>
-      <c r="AB26" s="55"/>
-      <c r="AC26" s="55"/>
-      <c r="AD26" s="55"/>
-      <c r="AE26" s="55"/>
-      <c r="AF26" s="55"/>
-      <c r="AG26" s="55"/>
-      <c r="AH26" s="55"/>
-      <c r="AI26" s="55"/>
-      <c r="AJ26" s="55"/>
-      <c r="AK26" s="55" t="s">
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="T26" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="30"/>
+      <c r="AD26" s="30"/>
+      <c r="AE26" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF26" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG26" s="30"/>
+      <c r="AH26" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI26" s="30"/>
+      <c r="AJ26" s="30"/>
+      <c r="AK26" s="30" t="s">
         <v>12</v>
       </c>
       <c r="AL26" s="34">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="8:38" ht="15.75">
@@ -2812,13 +2798,25 @@
       <c r="J27" s="14">
         <v>46220</v>
       </c>
-      <c r="K27" s="35"/>
-      <c r="L27" s="35"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="15"/>
+      <c r="K27" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="N27" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
+      <c r="P27" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q27" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="R27" s="15"/>
       <c r="S27" s="15"/>
       <c r="T27" s="15"/>
@@ -2841,7 +2839,7 @@
       <c r="AK27" s="15"/>
       <c r="AL27" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="8:38" ht="15.75">
@@ -3440,19 +3438,19 @@
       <c r="J42" s="47"/>
       <c r="K42" s="21">
         <f>COUNTA(K11:K41)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L42" s="21">
         <f t="shared" ref="L42:AK42" si="1">COUNTA(L11:L41)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M42" s="21">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N42" s="21">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O42" s="21">
         <f t="shared" si="1"/>
@@ -3460,11 +3458,11 @@
       </c>
       <c r="P42" s="21">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q42" s="21">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R42" s="21">
         <f t="shared" si="1"/>
@@ -3520,11 +3518,11 @@
       </c>
       <c r="AE42" s="21">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF42" s="21">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG42" s="21">
         <f t="shared" si="1"/>
@@ -3532,7 +3530,7 @@
       </c>
       <c r="AH42" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" s="21"/>
       <c r="AJ42" s="21"/>
